--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y960"/>
+  <dimension ref="A1:Y966"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>45147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>43802</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>44520</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44585</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>43433</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>43860</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>43860</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44120</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>44449</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44455</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44512</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44690</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44872</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>44879</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45140</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43334</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43339</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43339</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>43348</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>43349</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43349</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>43353</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>43356</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>43358</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>43360</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>43362</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43363</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>43377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>43388</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>43390</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43393</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>43393</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>43395</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43398</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>43412</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43418</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43420</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43425</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43433</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43433</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43433</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43434</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43436</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43437</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43442</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43451</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43454</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43462</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43464</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43464</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43464</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43473</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43474</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43479</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43480</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43482</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43485</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43486</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43489</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43494</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43496</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>43501</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>43504</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>43507</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>43507</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>43507</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43510</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43510</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43524</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43530</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>43532</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>43538</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>43546</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>43556</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>43556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>43578</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>43578</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>43578</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>43585</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>43592</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43594</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>43601</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>43602</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>43605</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>43606</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>43626</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>43649</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>43653</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>43662</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>43664</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>43670</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>43676</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>43684</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>43689</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>43689</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>43690</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43692</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43700</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43700</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43705</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43705</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>43705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>43705</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43708</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43710</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43726</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43727</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43731</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43731</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43731</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43731</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43739</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>43739</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>43741</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>43745</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>43748</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>43761</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>43765</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>43770</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>43774</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>43774</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>43784</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>43784</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43786</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43787</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>43789</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43795</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>43795</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>43796</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>43796</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43798</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43800</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>43829</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>43833</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>43842</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43845</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43846</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43854</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43860</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43860</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43860</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>43861</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>43861</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>43865</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>43865</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>43867</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>43868</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>43868</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>43868</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>43872</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>43878</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>43879</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>43881</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>43886</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>43892</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>43893</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>43893</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>43894</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>43899</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>43899</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43899</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>43901</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>43901</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>43901</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>43902</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>43903</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>43916</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>43920</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>43923</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>43927</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43929</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>43963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>43966</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>43974</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>43974</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>43979</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43980</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43986</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>43992</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>44004</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>44004</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44010</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>44040</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44042</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44046</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44048</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>44048</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44054</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44055</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44060</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44060</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44062</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44068</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44074</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44075</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44082</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44084</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44088</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44089</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44090</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44105</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44116</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44120</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44125</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44137</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44138</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44145</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>44147</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44154</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44160</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>44161</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>44161</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44161</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>44161</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44161</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44164</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44165</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44173</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44175</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44179</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44180</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44181</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44182</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44195</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44195</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>44195</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44201</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44201</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44204</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44206</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44206</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44215</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44218</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44218</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44220</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44221</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>44222</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44229</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44236</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44237</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44238</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44245</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44257</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44257</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>44265</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44267</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44267</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44267</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44270</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44273</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44280</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44294</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44295</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44299</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44299</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44299</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44299</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44306</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44306</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44306</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44309</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>44312</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>44312</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>44313</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44313</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44313</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>44314</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>44319</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>44319</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>44320</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>44325</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>44333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>44334</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44336</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44349</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44351</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44354</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44354</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44368</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44368</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44371</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44391</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44391</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44393</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44393</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44403</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44404</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44412</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44417</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44418</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44419</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44421</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44439</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44441</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44442</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44443</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44447</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44447</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44448</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44448</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44453</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44455</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44460</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44462</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44464</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44466</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44469</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44470</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44474</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44474</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44474</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44474</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44477</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44477</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44477</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44480</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44488</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44488</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44488</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>44488</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>44488</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>44488</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>44488</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>44490</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>44491</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>44497</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>44497</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>44497</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44497</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44501</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44501</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44503</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>44506</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44509</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44512</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44512</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>44512</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>44512</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44512</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44512</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44512</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44512</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44514</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44515</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>44515</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>44517</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44518</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44520</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44524</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44524</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44530</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44531</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44532</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>44533</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44533</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>44533</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>44543</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44543</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44552</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44553</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44558</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44565</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44565</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44566</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44567</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>44567</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44578</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44579</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44587</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44588</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44594</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44599</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44606</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44606</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44607</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44607</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44607</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44609</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44609</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44609</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44609</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44613</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44613</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44621</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44621</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44624</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44626</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44636</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44636</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44638</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44638</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44638</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44638</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>44638</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>44641</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>44642</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44648</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44649</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44655</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>44655</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>44655</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>44656</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44656</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44656</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44657</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>44657</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>44658</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44658</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44663</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>44663</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>44663</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>44663</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>44663</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>44670</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>44670</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44672</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44672</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44674</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44677</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44678</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44678</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44679</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>44679</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>44685</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44686</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44686</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>44692</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>44697</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>44698</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44699</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>44705</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44713</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44715</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44719</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44720</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44724</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>44725</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>44726</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44733</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44735</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>44740</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>44741</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>44749</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>44750</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>44762</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>44763</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44768</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>44771</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>44771</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>44772</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44775</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>44776</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>44776</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44776</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44781</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>44790</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44796</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>44800</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>44805</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>44809</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>44809</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44809</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44810</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44810</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44812</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44817</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>44817</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>44823</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>44824</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44830</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>44831</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>44831</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44837</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>44837</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>44838</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>44838</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>44839</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44841</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>44845</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>44846</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>44854</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>44855</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>44858</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>44858</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>44859</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>44861</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>44861</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44873</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>44879</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>44880</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44880</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44881</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44881</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>44881</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>44881</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>44882</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44882</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>44882</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>44882</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>44882</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44882</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>44883</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>44887</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>44887</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>44887</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>44888</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>44893</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>44893</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>44893</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>44894</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>44894</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44895</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>44895</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>44896</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>44896</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>44908</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>44908</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>44909</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44911</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44914</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>44916</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>44916</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>44917</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>44929</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44931</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>44944</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>44945</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44945</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44945</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>44947</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44947</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>44951</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>44951</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>44959</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>44959</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>44959</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>44959</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44959</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>44961</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>44964</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>44965</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>44966</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>44967</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>44967</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44970</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44971</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>44971</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>44971</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44971</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44971</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>44977</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>44978</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>44992</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44994</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>44999</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45002</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45002</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45002</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45006</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45006</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>45006</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45007</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45008</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45008</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45009</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45015</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45021</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45022</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45033</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45033</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45035</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45037</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45038</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45038</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>45038</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45038</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45040</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>45041</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45042</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45043</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45043</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45043</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45043</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45044</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45048</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45053</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45059</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45062</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45068</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45068</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45069</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45069</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45070</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45070</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45070</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45070</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45070</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45070</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45071</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45071</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45071</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45072</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45075</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45078</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45079</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45084</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45084</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45084</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>45084</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45084</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45084</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45084</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45085</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45085</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45087</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41537,7 +41537,7 @@
         <v>45087</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45087</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45087</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45089</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45091</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45092</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45092</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45093</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45093</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42335,7 +42335,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45097</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45099</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>45104</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45104</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45104</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45112</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45114</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45120</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45124</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45132</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45132</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45133</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45134</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45134</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45134</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45134</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>45134</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45134</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45134</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45134</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45139</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45140</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45140</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45140</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45140</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45140</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45140</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45141</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45147</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>45147</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45152</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45153</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45153</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>45154</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>45154</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45157</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45157</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>45157</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45158</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45159</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45159</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45160</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45160</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45161</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45161</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45161</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45161</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45162</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45162</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45162</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45162</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45162</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45162</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45162</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45162</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45162</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45162</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45162</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45162</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45162</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45163</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45163</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45163</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>45163</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>45163</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45163</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45163</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45166</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45166</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45166</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45166</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45166</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45166</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45166</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45167</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45167</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>45167</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45167</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>45168</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45168</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45168</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45169</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>45170</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45173</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45173</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47584,7 +47584,7 @@
         <v>45173</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>45173</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>45173</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45174</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>45176</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>45176</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>45180</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45180</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>45181</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45182</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45187</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45187</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45189</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45189</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45190</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45190</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45190</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45191</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45194</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45194</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45194</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45196</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45197</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45199</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45199</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45201</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45203</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45209</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45211</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45211</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45212</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45215</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45217</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45217</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45217</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45218</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45222</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45223</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45224</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45224</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45224</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45225</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45225</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>45225</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>45225</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45225</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45225</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>45225</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>45225</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45225</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51522,7 +51522,7 @@
         <v>45226</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45227</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45227</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45227</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45227</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51807,7 +51807,7 @@
         <v>45227</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>45227</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51914,14 +51914,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 53666-2023</t>
+          <t>A 53664-2023</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51971,14 +51971,14 @@
     <row r="888" ht="15" customHeight="1">
       <c r="A888" t="inlineStr">
         <is>
-          <t>A 53664-2023</t>
+          <t>A 53666-2023</t>
         </is>
       </c>
       <c r="B888" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52035,7 +52035,7 @@
         <v>45231</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45231</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52159,7 +52159,7 @@
         <v>45233</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52216,7 +52216,7 @@
         <v>45233</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>45233</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>45233</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>45233</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52437,14 +52437,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 54362-2023</t>
+          <t>A 54577-2023</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52494,14 +52494,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 54405-2023</t>
+          <t>A 54581-2023</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52551,14 +52551,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 54577-2023</t>
+          <t>A 54362-2023</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52608,14 +52608,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 54581-2023</t>
+          <t>A 54405-2023</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52628,7 +52628,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52665,14 +52665,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 54903-2023</t>
+          <t>A 54699-2023</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52722,14 +52722,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 54699-2023</t>
+          <t>A 54903-2023</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52779,14 +52779,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 54909-2023</t>
+          <t>A 54906-2023</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52836,14 +52836,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 54915-2023</t>
+          <t>A 54912-2023</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52856,7 +52856,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -52893,14 +52893,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 54906-2023</t>
+          <t>A 54904-2023</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -52950,14 +52950,14 @@
     <row r="905" ht="15" customHeight="1">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A 54912-2023</t>
+          <t>A 54914-2023</t>
         </is>
       </c>
       <c r="B905" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -53007,14 +53007,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 54955-2023</t>
+          <t>A 54957-2023</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -53064,14 +53064,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 54957-2023</t>
+          <t>A 54909-2023</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -53121,14 +53121,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 54904-2023</t>
+          <t>A 54915-2023</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         </is>
       </c>
       <c r="G908" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -53178,14 +53178,14 @@
     <row r="909" ht="15" customHeight="1">
       <c r="A909" t="inlineStr">
         <is>
-          <t>A 54914-2023</t>
+          <t>A 54955-2023</t>
         </is>
       </c>
       <c r="B909" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         </is>
       </c>
       <c r="G909" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H909" t="n">
         <v>0</v>
@@ -53235,14 +53235,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 55160-2023</t>
+          <t>A 55267-2023</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53292,14 +53292,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 55264-2023</t>
+          <t>A 55160-2023</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53349,14 +53349,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 55269-2023</t>
+          <t>A 55264-2023</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53406,14 +53406,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 55309-2023</t>
+          <t>A 55269-2023</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -53463,14 +53463,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 55267-2023</t>
+          <t>A 55309-2023</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -53520,14 +53520,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 55763-2023</t>
+          <t>A 55765-2023</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53577,14 +53577,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 55765-2023</t>
+          <t>A 55763-2023</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53641,7 +53641,7 @@
         <v>45242</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53698,7 +53698,7 @@
         <v>45242</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>45243</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>45244</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>45244</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45244</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53976,14 +53976,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 56778-2023</t>
+          <t>A 56793-2023</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54033,14 +54033,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 56786-2023</t>
+          <t>A 56779-2023</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54090,14 +54090,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 56794-2023</t>
+          <t>A 56791-2023</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54147,14 +54147,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 56802-2023</t>
+          <t>A 56795-2023</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54204,14 +54204,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 56793-2023</t>
+          <t>A 56799-2023</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54261,14 +54261,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 56779-2023</t>
+          <t>A 56778-2023</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54318,14 +54318,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 56791-2023</t>
+          <t>A 56786-2023</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54375,14 +54375,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 56795-2023</t>
+          <t>A 56794-2023</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54432,14 +54432,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 56799-2023</t>
+          <t>A 56802-2023</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54496,7 +54496,7 @@
         <v>45244</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54553,7 +54553,7 @@
         <v>45244</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54667,7 +54667,7 @@
         <v>45244</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>45244</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54781,7 +54781,7 @@
         <v>45245</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -54838,7 +54838,7 @@
         <v>45245</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -54888,14 +54888,14 @@
     <row r="939" ht="15" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>A 57196-2023</t>
+          <t>A 57170-2023</t>
         </is>
       </c>
       <c r="B939" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -54945,14 +54945,14 @@
     <row r="940" ht="15" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>A 57170-2023</t>
+          <t>A 57204-2023</t>
         </is>
       </c>
       <c r="B940" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -55002,14 +55002,14 @@
     <row r="941" ht="15" customHeight="1">
       <c r="A941" t="inlineStr">
         <is>
-          <t>A 57204-2023</t>
+          <t>A 57196-2023</t>
         </is>
       </c>
       <c r="B941" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="H941" t="n">
         <v>0</v>
@@ -55066,7 +55066,7 @@
         <v>45246</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55123,7 +55123,7 @@
         <v>45246</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55180,7 +55180,7 @@
         <v>45246</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55230,14 +55230,14 @@
     <row r="945" ht="15" customHeight="1">
       <c r="A945" t="inlineStr">
         <is>
-          <t>A 57854-2023</t>
+          <t>A 57917-2023</t>
         </is>
       </c>
       <c r="B945" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         </is>
       </c>
       <c r="G945" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -55287,14 +55287,14 @@
     <row r="946" ht="15" customHeight="1">
       <c r="A946" t="inlineStr">
         <is>
-          <t>A 57916-2023</t>
+          <t>A 57854-2023</t>
         </is>
       </c>
       <c r="B946" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         </is>
       </c>
       <c r="G946" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -55344,14 +55344,14 @@
     <row r="947" ht="15" customHeight="1">
       <c r="A947" t="inlineStr">
         <is>
-          <t>A 57917-2023</t>
+          <t>A 57916-2023</t>
         </is>
       </c>
       <c r="B947" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         </is>
       </c>
       <c r="G947" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -55408,7 +55408,7 @@
         <v>45250</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55458,14 +55458,14 @@
     <row r="949" ht="15" customHeight="1">
       <c r="A949" t="inlineStr">
         <is>
-          <t>A 58401-2023</t>
+          <t>A 58283-2023</t>
         </is>
       </c>
       <c r="B949" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -55515,14 +55515,14 @@
     <row r="950" ht="15" customHeight="1">
       <c r="A950" t="inlineStr">
         <is>
-          <t>A 58426-2023</t>
+          <t>A 58403-2023</t>
         </is>
       </c>
       <c r="B950" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         </is>
       </c>
       <c r="G950" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H950" t="n">
         <v>0</v>
@@ -55572,14 +55572,14 @@
     <row r="951" ht="15" customHeight="1">
       <c r="A951" t="inlineStr">
         <is>
-          <t>A 58283-2023</t>
+          <t>A 58401-2023</t>
         </is>
       </c>
       <c r="B951" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         </is>
       </c>
       <c r="G951" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -55629,14 +55629,14 @@
     <row r="952" ht="15" customHeight="1">
       <c r="A952" t="inlineStr">
         <is>
-          <t>A 58403-2023</t>
+          <t>A 58426-2023</t>
         </is>
       </c>
       <c r="B952" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -55686,14 +55686,14 @@
     <row r="953" ht="15" customHeight="1">
       <c r="A953" t="inlineStr">
         <is>
-          <t>A 58917-2023</t>
+          <t>A 59036-2023</t>
         </is>
       </c>
       <c r="B953" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         </is>
       </c>
       <c r="G953" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -55750,7 +55750,7 @@
         <v>45252</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -55800,14 +55800,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 59036-2023</t>
+          <t>A 58917-2023</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -55820,7 +55820,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -55864,7 +55864,7 @@
         <v>45254</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45257</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>45257</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56035,7 +56035,7 @@
         <v>45257</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56082,62 +56082,404 @@
       </c>
       <c r="R959" s="2" t="inlineStr"/>
     </row>
-    <row r="960">
+    <row r="960" ht="15" customHeight="1">
       <c r="A960" t="inlineStr">
         <is>
-          <t>A 60016-2023</t>
+          <t>A 60274-2023</t>
         </is>
       </c>
       <c r="B960" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C960" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G960" t="n">
+        <v>2</v>
+      </c>
+      <c r="H960" t="n">
+        <v>0</v>
+      </c>
+      <c r="I960" t="n">
+        <v>0</v>
+      </c>
+      <c r="J960" t="n">
+        <v>0</v>
+      </c>
+      <c r="K960" t="n">
+        <v>0</v>
+      </c>
+      <c r="L960" t="n">
+        <v>0</v>
+      </c>
+      <c r="M960" t="n">
+        <v>0</v>
+      </c>
+      <c r="N960" t="n">
+        <v>0</v>
+      </c>
+      <c r="O960" t="n">
+        <v>0</v>
+      </c>
+      <c r="P960" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q960" t="n">
+        <v>0</v>
+      </c>
+      <c r="R960" s="2" t="inlineStr"/>
+    </row>
+    <row r="961" ht="15" customHeight="1">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>A 60016-2023</t>
+        </is>
+      </c>
+      <c r="B961" s="1" t="n">
         <v>45258</v>
       </c>
-      <c r="D960" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E960" t="inlineStr">
-        <is>
-          <t>ULRICEHAMN</t>
-        </is>
-      </c>
-      <c r="G960" t="n">
+      <c r="C961" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G961" t="n">
         <v>0.8</v>
       </c>
-      <c r="H960" t="n">
-        <v>0</v>
-      </c>
-      <c r="I960" t="n">
-        <v>0</v>
-      </c>
-      <c r="J960" t="n">
-        <v>0</v>
-      </c>
-      <c r="K960" t="n">
-        <v>0</v>
-      </c>
-      <c r="L960" t="n">
-        <v>0</v>
-      </c>
-      <c r="M960" t="n">
-        <v>0</v>
-      </c>
-      <c r="N960" t="n">
-        <v>0</v>
-      </c>
-      <c r="O960" t="n">
-        <v>0</v>
-      </c>
-      <c r="P960" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q960" t="n">
-        <v>0</v>
-      </c>
-      <c r="R960" s="2" t="inlineStr"/>
+      <c r="H961" t="n">
+        <v>0</v>
+      </c>
+      <c r="I961" t="n">
+        <v>0</v>
+      </c>
+      <c r="J961" t="n">
+        <v>0</v>
+      </c>
+      <c r="K961" t="n">
+        <v>0</v>
+      </c>
+      <c r="L961" t="n">
+        <v>0</v>
+      </c>
+      <c r="M961" t="n">
+        <v>0</v>
+      </c>
+      <c r="N961" t="n">
+        <v>0</v>
+      </c>
+      <c r="O961" t="n">
+        <v>0</v>
+      </c>
+      <c r="P961" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q961" t="n">
+        <v>0</v>
+      </c>
+      <c r="R961" s="2" t="inlineStr"/>
+    </row>
+    <row r="962" ht="15" customHeight="1">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>A 60084-2023</t>
+        </is>
+      </c>
+      <c r="B962" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C962" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G962" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H962" t="n">
+        <v>0</v>
+      </c>
+      <c r="I962" t="n">
+        <v>0</v>
+      </c>
+      <c r="J962" t="n">
+        <v>0</v>
+      </c>
+      <c r="K962" t="n">
+        <v>0</v>
+      </c>
+      <c r="L962" t="n">
+        <v>0</v>
+      </c>
+      <c r="M962" t="n">
+        <v>0</v>
+      </c>
+      <c r="N962" t="n">
+        <v>0</v>
+      </c>
+      <c r="O962" t="n">
+        <v>0</v>
+      </c>
+      <c r="P962" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q962" t="n">
+        <v>0</v>
+      </c>
+      <c r="R962" s="2" t="inlineStr"/>
+    </row>
+    <row r="963" ht="15" customHeight="1">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>A 60277-2023</t>
+        </is>
+      </c>
+      <c r="B963" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C963" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G963" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H963" t="n">
+        <v>0</v>
+      </c>
+      <c r="I963" t="n">
+        <v>0</v>
+      </c>
+      <c r="J963" t="n">
+        <v>0</v>
+      </c>
+      <c r="K963" t="n">
+        <v>0</v>
+      </c>
+      <c r="L963" t="n">
+        <v>0</v>
+      </c>
+      <c r="M963" t="n">
+        <v>0</v>
+      </c>
+      <c r="N963" t="n">
+        <v>0</v>
+      </c>
+      <c r="O963" t="n">
+        <v>0</v>
+      </c>
+      <c r="P963" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q963" t="n">
+        <v>0</v>
+      </c>
+      <c r="R963" s="2" t="inlineStr"/>
+    </row>
+    <row r="964" ht="15" customHeight="1">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>A 60291-2023</t>
+        </is>
+      </c>
+      <c r="B964" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C964" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G964" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H964" t="n">
+        <v>0</v>
+      </c>
+      <c r="I964" t="n">
+        <v>0</v>
+      </c>
+      <c r="J964" t="n">
+        <v>0</v>
+      </c>
+      <c r="K964" t="n">
+        <v>0</v>
+      </c>
+      <c r="L964" t="n">
+        <v>0</v>
+      </c>
+      <c r="M964" t="n">
+        <v>0</v>
+      </c>
+      <c r="N964" t="n">
+        <v>0</v>
+      </c>
+      <c r="O964" t="n">
+        <v>0</v>
+      </c>
+      <c r="P964" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q964" t="n">
+        <v>0</v>
+      </c>
+      <c r="R964" s="2" t="inlineStr"/>
+    </row>
+    <row r="965" ht="15" customHeight="1">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>A 60290-2023</t>
+        </is>
+      </c>
+      <c r="B965" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C965" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G965" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H965" t="n">
+        <v>0</v>
+      </c>
+      <c r="I965" t="n">
+        <v>0</v>
+      </c>
+      <c r="J965" t="n">
+        <v>0</v>
+      </c>
+      <c r="K965" t="n">
+        <v>0</v>
+      </c>
+      <c r="L965" t="n">
+        <v>0</v>
+      </c>
+      <c r="M965" t="n">
+        <v>0</v>
+      </c>
+      <c r="N965" t="n">
+        <v>0</v>
+      </c>
+      <c r="O965" t="n">
+        <v>0</v>
+      </c>
+      <c r="P965" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q965" t="n">
+        <v>0</v>
+      </c>
+      <c r="R965" s="2" t="inlineStr"/>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>A 60293-2023</t>
+        </is>
+      </c>
+      <c r="B966" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C966" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G966" t="n">
+        <v>1</v>
+      </c>
+      <c r="H966" t="n">
+        <v>0</v>
+      </c>
+      <c r="I966" t="n">
+        <v>0</v>
+      </c>
+      <c r="J966" t="n">
+        <v>0</v>
+      </c>
+      <c r="K966" t="n">
+        <v>0</v>
+      </c>
+      <c r="L966" t="n">
+        <v>0</v>
+      </c>
+      <c r="M966" t="n">
+        <v>0</v>
+      </c>
+      <c r="N966" t="n">
+        <v>0</v>
+      </c>
+      <c r="O966" t="n">
+        <v>0</v>
+      </c>
+      <c r="P966" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q966" t="n">
+        <v>0</v>
+      </c>
+      <c r="R966" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -564,7 +564,7 @@
         <v>45147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>43802</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>44520</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44585</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>43433</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>43860</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>43860</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44120</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>44449</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44455</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44512</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44690</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44872</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>44879</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45140</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43334</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43339</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43339</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>43348</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>43349</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43349</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>43353</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>43356</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>43358</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>43360</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>43362</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43363</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>43377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>43388</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>43390</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43393</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>43393</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>43395</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43398</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>43412</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43418</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43420</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43425</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43433</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43433</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43433</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43434</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43436</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43437</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43442</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43451</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43454</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43462</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43464</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43464</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43464</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43473</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43474</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43479</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43480</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43482</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43485</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43486</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43489</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43494</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43496</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>43501</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>43504</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>43507</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>43507</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>43507</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43510</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43510</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43524</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43530</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>43532</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>43538</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>43546</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>43556</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>43556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>43578</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>43578</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>43578</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>43585</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>43592</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43594</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>43601</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>43602</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>43605</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>43606</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>43626</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>43649</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>43653</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>43662</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>43664</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>43670</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>43676</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>43684</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>43689</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>43689</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>43690</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43692</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43700</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43700</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43705</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43705</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>43705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>43705</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43708</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43710</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43726</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43727</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43731</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43731</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43731</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43731</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43739</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>43739</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>43741</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>43745</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>43748</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>43761</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>43765</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>43770</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>43774</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>43774</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>43784</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>43784</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43786</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43787</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>43789</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43795</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>43795</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>43796</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>43796</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43798</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43800</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>43829</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>43833</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>43842</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43845</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43846</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43854</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43860</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43860</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43860</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>43861</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>43861</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>43865</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>43865</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>43867</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>43868</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>43868</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>43868</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>43872</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>43878</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>43879</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>43881</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>43886</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>43892</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>43893</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>43893</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>43894</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>43899</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>43899</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43899</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>43901</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>43901</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>43901</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>43902</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>43903</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>43916</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>43920</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>43923</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>43927</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43929</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>43963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>43966</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>43974</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>43974</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>43979</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43980</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43986</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>43992</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>44004</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>44004</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44010</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>44040</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44042</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44046</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44048</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>44048</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44054</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44055</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44060</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44060</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44062</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44068</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44074</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44075</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44082</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44084</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44088</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44089</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44090</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44105</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44116</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44120</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44125</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44137</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44138</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44145</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>44147</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44154</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44160</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>44161</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>44161</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44161</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>44161</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44161</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44164</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44165</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44173</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44175</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44179</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44180</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44181</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44182</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44195</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44195</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>44195</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44201</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44201</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44204</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44206</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44206</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44215</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44218</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44218</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44220</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44221</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>44222</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44229</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44236</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44237</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44238</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44245</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44257</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44257</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>44265</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44267</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44267</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44267</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44270</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44273</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44280</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44294</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44295</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44299</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44299</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44299</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44299</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44306</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44306</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44306</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44309</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>44312</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>44312</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>44313</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44313</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44313</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>44314</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>44319</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>44319</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>44320</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>44325</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>44333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>44334</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44336</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44349</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44351</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44354</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44354</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44368</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44368</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44371</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44391</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44391</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44393</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44393</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44403</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44404</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44412</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44417</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44418</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44419</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44421</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44439</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44441</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44442</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44443</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44447</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44447</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44448</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44448</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44453</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44455</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44460</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44462</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44464</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44466</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44469</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44470</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44474</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44474</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44474</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44474</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44477</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44477</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44477</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44480</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44488</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44488</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44488</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>44488</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>44488</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>44488</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>44488</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>44490</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>44491</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>44497</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>44497</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>44497</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44497</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44501</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44501</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44503</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>44506</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44509</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44512</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44512</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>44512</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>44512</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44512</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44512</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44512</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44512</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44514</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44515</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>44515</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>44517</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44518</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44520</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44524</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44524</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44530</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44531</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44532</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>44533</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44533</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>44533</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>44543</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44543</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44552</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44553</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44558</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44565</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44565</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44566</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44567</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>44567</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44578</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44579</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44587</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44588</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44594</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44599</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44606</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44606</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44607</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44607</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44607</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44609</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44609</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44609</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44609</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44613</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44613</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44621</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44621</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44624</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44626</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44636</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44636</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44638</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44638</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44638</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44638</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>44638</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>44641</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>44642</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44648</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44649</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44655</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>44655</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>44655</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>44656</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44656</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44656</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44657</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>44657</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>44658</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44658</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44663</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>44663</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>44663</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>44663</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>44663</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>44670</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>44670</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44672</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44672</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44674</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44677</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44678</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44678</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44679</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>44679</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>44685</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44686</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44686</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>44692</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>44697</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>44698</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44699</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>44705</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44713</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44715</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44719</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44720</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44724</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>44725</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>44726</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44733</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44735</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>44740</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>44741</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>44749</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>44750</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>44762</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>44763</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44768</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>44771</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>44771</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>44772</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44775</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>44776</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>44776</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44776</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44781</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>44790</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44796</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>44800</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>44805</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>44809</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>44809</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44809</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44810</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44810</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44812</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44817</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>44817</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>44823</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>44824</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44830</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>44831</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>44831</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44837</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>44837</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>44838</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>44838</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>44839</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44841</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>44845</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>44846</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>44854</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>44855</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>44858</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>44858</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>44859</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>44861</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>44861</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44873</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>44879</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>44880</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44880</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44881</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44881</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>44881</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>44881</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>44882</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44882</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>44882</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>44882</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>44882</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44882</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>44883</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>44887</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>44887</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>44887</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>44888</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>44893</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>44893</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>44893</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>44894</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>44894</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44895</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>44895</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>44896</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>44896</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>44908</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>44908</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>44909</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44911</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44914</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>44916</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>44916</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>44917</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>44929</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44931</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>44944</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>44945</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44945</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44945</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>44947</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44947</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>44951</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>44951</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>44959</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>44959</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>44959</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>44959</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44959</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>44961</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>44964</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>44965</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>44966</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>44967</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>44967</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44970</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44971</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>44971</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>44971</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44971</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44971</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>44977</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>44978</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>44992</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44994</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>44999</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45002</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45002</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45002</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45006</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45006</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>45006</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45007</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45008</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45008</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45009</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45015</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45021</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45022</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45033</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45033</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45035</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45037</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45038</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45038</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>45038</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45038</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45040</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>45041</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45042</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45043</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45043</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45043</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45043</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45044</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45048</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45053</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45059</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45062</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45068</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45068</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45069</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45069</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45070</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45070</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45070</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45070</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45070</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45070</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45071</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45071</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45071</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45072</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45075</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45078</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45079</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45084</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45084</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45084</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>45084</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45084</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45084</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45084</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45085</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45085</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45087</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41537,7 +41537,7 @@
         <v>45087</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45087</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45087</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45089</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45091</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45092</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45092</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45093</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45093</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42335,7 +42335,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45097</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45099</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>45104</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45104</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45104</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45112</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45114</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45120</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45124</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45132</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45132</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45133</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45134</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45134</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45134</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45134</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>45134</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45134</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45134</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45134</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45139</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45140</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45140</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45140</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45140</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45140</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45140</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45141</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45147</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>45147</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45152</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45153</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45153</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>45154</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>45154</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45157</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45157</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>45157</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45158</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45159</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45159</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45160</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45160</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45161</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45161</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45161</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45161</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45162</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45162</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45162</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45162</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45162</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45162</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45162</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45162</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45162</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45162</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45162</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45162</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45162</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45163</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45163</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45163</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>45163</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>45163</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45163</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45163</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45166</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45166</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45166</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45166</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45166</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45166</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45166</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45167</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45167</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>45167</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45167</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>45168</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45168</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45168</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45169</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>45170</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45173</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45173</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47584,7 +47584,7 @@
         <v>45173</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>45173</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>45173</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45174</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>45176</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>45176</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>45180</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45180</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>45181</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45182</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45187</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45187</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45189</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45189</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45190</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45190</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45190</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45191</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45194</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45194</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45194</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45196</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45197</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45199</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45199</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45201</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45203</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45209</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45211</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45211</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45212</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45215</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45217</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45217</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45217</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45218</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45222</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45223</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45224</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45224</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45224</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45225</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45225</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>45225</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>45225</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45225</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45225</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>45225</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>45225</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45225</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51522,7 +51522,7 @@
         <v>45226</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45227</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45227</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45227</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45227</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51807,7 +51807,7 @@
         <v>45227</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>45227</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>45230</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>45230</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52035,7 +52035,7 @@
         <v>45231</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45231</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52159,7 +52159,7 @@
         <v>45231</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52216,7 +52216,7 @@
         <v>45231</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>45231</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>45233</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52380,14 +52380,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 54359-2023</t>
+          <t>A 54405-2023</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52400,7 +52400,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52437,14 +52437,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 54405-2023</t>
+          <t>A 54389-2023</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52494,14 +52494,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 54575-2023</t>
+          <t>A 54403-2023</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52551,14 +52551,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 54577-2023</t>
+          <t>A 54407-2023</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52608,14 +52608,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 54581-2023</t>
+          <t>A 54359-2023</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52628,7 +52628,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52665,14 +52665,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 54389-2023</t>
+          <t>A 54577-2023</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52722,14 +52722,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 54403-2023</t>
+          <t>A 54581-2023</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52779,14 +52779,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 54407-2023</t>
+          <t>A 54575-2023</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>2</v>
+        <v>12.5</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52843,7 +52843,7 @@
         <v>45236</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52893,14 +52893,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 54903-2023</t>
+          <t>A 54904-2023</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>6.4</v>
+        <v>0.2</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -52950,14 +52950,14 @@
     <row r="905" ht="15" customHeight="1">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A 54909-2023</t>
+          <t>A 54914-2023</t>
         </is>
       </c>
       <c r="B905" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -53007,14 +53007,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 54915-2023</t>
+          <t>A 54909-2023</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -53064,14 +53064,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 54906-2023</t>
+          <t>A 54915-2023</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -53121,14 +53121,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 54912-2023</t>
+          <t>A 54906-2023</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         </is>
       </c>
       <c r="G908" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -53178,14 +53178,14 @@
     <row r="909" ht="15" customHeight="1">
       <c r="A909" t="inlineStr">
         <is>
-          <t>A 54904-2023</t>
+          <t>A 54912-2023</t>
         </is>
       </c>
       <c r="B909" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         </is>
       </c>
       <c r="G909" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="H909" t="n">
         <v>0</v>
@@ -53235,14 +53235,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 54914-2023</t>
+          <t>A 54903-2023</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53299,7 +53299,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53356,7 +53356,7 @@
         <v>45236</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53406,14 +53406,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 55160-2023</t>
+          <t>A 55267-2023</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -53463,14 +53463,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 55264-2023</t>
+          <t>A 55160-2023</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -53520,14 +53520,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 55269-2023</t>
+          <t>A 55309-2023</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53540,7 +53540,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53577,14 +53577,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 55267-2023</t>
+          <t>A 55264-2023</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53597,7 +53597,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53634,14 +53634,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 55309-2023</t>
+          <t>A 55269-2023</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53654,7 +53654,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53691,14 +53691,14 @@
     <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>A 55763-2023</t>
+          <t>A 55765-2023</t>
         </is>
       </c>
       <c r="B918" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53748,14 +53748,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 55765-2023</t>
+          <t>A 55763-2023</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>45242</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>45242</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45243</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53976,14 +53976,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 56717-2023</t>
+          <t>A 56779-2023</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54033,14 +54033,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 56772-2023</t>
+          <t>A 56791-2023</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54090,14 +54090,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 56776-2023</t>
+          <t>A 56795-2023</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54147,14 +54147,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 56778-2023</t>
+          <t>A 56799-2023</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54204,14 +54204,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 56786-2023</t>
+          <t>A 56775-2023</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54261,14 +54261,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 56794-2023</t>
+          <t>A 56780-2023</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54318,14 +54318,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 56802-2023</t>
+          <t>A 56784-2023</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54375,14 +54375,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 56793-2023</t>
+          <t>A 56796-2023</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54432,14 +54432,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 56779-2023</t>
+          <t>A 56804-2023</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54489,14 +54489,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 56791-2023</t>
+          <t>A 56717-2023</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54546,14 +54546,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 56795-2023</t>
+          <t>A 56772-2023</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54603,14 +54603,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 56799-2023</t>
+          <t>A 56776-2023</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54660,14 +54660,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 56775-2023</t>
+          <t>A 56793-2023</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54717,14 +54717,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 56780-2023</t>
+          <t>A 56778-2023</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54737,7 +54737,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54774,14 +54774,14 @@
     <row r="937" ht="15" customHeight="1">
       <c r="A937" t="inlineStr">
         <is>
-          <t>A 56784-2023</t>
+          <t>A 56786-2023</t>
         </is>
       </c>
       <c r="B937" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
         </is>
       </c>
       <c r="G937" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="H937" t="n">
         <v>0</v>
@@ -54831,14 +54831,14 @@
     <row r="938" ht="15" customHeight="1">
       <c r="A938" t="inlineStr">
         <is>
-          <t>A 56796-2023</t>
+          <t>A 56794-2023</t>
         </is>
       </c>
       <c r="B938" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         </is>
       </c>
       <c r="G938" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H938" t="n">
         <v>0</v>
@@ -54888,14 +54888,14 @@
     <row r="939" ht="15" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>A 56804-2023</t>
+          <t>A 56802-2023</t>
         </is>
       </c>
       <c r="B939" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -54945,14 +54945,14 @@
     <row r="940" ht="15" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>A 57173-2023</t>
+          <t>A 57215-2023</t>
         </is>
       </c>
       <c r="B940" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -55002,14 +55002,14 @@
     <row r="941" ht="15" customHeight="1">
       <c r="A941" t="inlineStr">
         <is>
-          <t>A 57215-2023</t>
+          <t>A 57196-2023</t>
         </is>
       </c>
       <c r="B941" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="H941" t="n">
         <v>0</v>
@@ -55059,14 +55059,14 @@
     <row r="942" ht="15" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>A 57196-2023</t>
+          <t>A 57170-2023</t>
         </is>
       </c>
       <c r="B942" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55116,14 +55116,14 @@
     <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
-          <t>A 57170-2023</t>
+          <t>A 57204-2023</t>
         </is>
       </c>
       <c r="B943" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55136,7 +55136,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -55173,14 +55173,14 @@
     <row r="944" ht="15" customHeight="1">
       <c r="A944" t="inlineStr">
         <is>
-          <t>A 57204-2023</t>
+          <t>A 57173-2023</t>
         </is>
       </c>
       <c r="B944" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -55230,14 +55230,14 @@
     <row r="945" ht="15" customHeight="1">
       <c r="A945" t="inlineStr">
         <is>
-          <t>A 57562-2023</t>
+          <t>A 58406-2023</t>
         </is>
       </c>
       <c r="B945" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         </is>
       </c>
       <c r="G945" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -55287,14 +55287,14 @@
     <row r="946" ht="15" customHeight="1">
       <c r="A946" t="inlineStr">
         <is>
-          <t>A 57571-2023</t>
+          <t>A 57562-2023</t>
         </is>
       </c>
       <c r="B946" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         </is>
       </c>
       <c r="G946" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -55344,14 +55344,14 @@
     <row r="947" ht="15" customHeight="1">
       <c r="A947" t="inlineStr">
         <is>
-          <t>A 58406-2023</t>
+          <t>A 57571-2023</t>
         </is>
       </c>
       <c r="B947" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         </is>
       </c>
       <c r="G947" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -55408,7 +55408,7 @@
         <v>45247</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55465,7 +55465,7 @@
         <v>45247</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55522,7 +55522,7 @@
         <v>45247</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55572,14 +55572,14 @@
     <row r="951" ht="15" customHeight="1">
       <c r="A951" t="inlineStr">
         <is>
-          <t>A 58204-2023</t>
+          <t>A 58283-2023</t>
         </is>
       </c>
       <c r="B951" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         </is>
       </c>
       <c r="G951" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -55629,14 +55629,14 @@
     <row r="952" ht="15" customHeight="1">
       <c r="A952" t="inlineStr">
         <is>
-          <t>A 58401-2023</t>
+          <t>A 58204-2023</t>
         </is>
       </c>
       <c r="B952" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -55686,14 +55686,14 @@
     <row r="953" ht="15" customHeight="1">
       <c r="A953" t="inlineStr">
         <is>
-          <t>A 58426-2023</t>
+          <t>A 58401-2023</t>
         </is>
       </c>
       <c r="B953" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         </is>
       </c>
       <c r="G953" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -55743,14 +55743,14 @@
     <row r="954" ht="15" customHeight="1">
       <c r="A954" t="inlineStr">
         <is>
-          <t>A 58283-2023</t>
+          <t>A 58426-2023</t>
         </is>
       </c>
       <c r="B954" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -55763,7 +55763,7 @@
         </is>
       </c>
       <c r="G954" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H954" t="n">
         <v>0</v>
@@ -55807,7 +55807,7 @@
         <v>45250</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -55864,7 +55864,7 @@
         <v>45252</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -55914,14 +55914,14 @@
     <row r="957" ht="15" customHeight="1">
       <c r="A957" t="inlineStr">
         <is>
-          <t>A 59036-2023</t>
+          <t>A 59075-2023</t>
         </is>
       </c>
       <c r="B957" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -55934,7 +55934,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H957" t="n">
         <v>0</v>
@@ -55971,14 +55971,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 59075-2023</t>
+          <t>A 59036-2023</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -55991,7 +55991,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56035,7 +56035,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56092,7 +56092,7 @@
         <v>45257</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56149,7 +56149,7 @@
         <v>45257</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56206,7 +56206,7 @@
         <v>45257</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56256,14 +56256,14 @@
     <row r="963" ht="15" customHeight="1">
       <c r="A963" t="inlineStr">
         <is>
-          <t>A 60016-2023</t>
+          <t>A 60084-2023</t>
         </is>
       </c>
       <c r="B963" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56276,7 +56276,7 @@
         </is>
       </c>
       <c r="G963" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="H963" t="n">
         <v>0</v>
@@ -56313,14 +56313,14 @@
     <row r="964" ht="15" customHeight="1">
       <c r="A964" t="inlineStr">
         <is>
-          <t>A 60084-2023</t>
+          <t>A 60016-2023</t>
         </is>
       </c>
       <c r="B964" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         </is>
       </c>
       <c r="G964" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="H964" t="n">
         <v>0</v>
@@ -56370,14 +56370,14 @@
     <row r="965" ht="15" customHeight="1">
       <c r="A965" t="inlineStr">
         <is>
-          <t>A 60277-2023</t>
+          <t>A 60293-2023</t>
         </is>
       </c>
       <c r="B965" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         </is>
       </c>
       <c r="G965" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -56427,14 +56427,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 60290-2023</t>
+          <t>A 60274-2023</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -56484,14 +56484,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 60293-2023</t>
+          <t>A 60290-2023</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56541,14 +56541,14 @@
     <row r="968" ht="15" customHeight="1">
       <c r="A968" t="inlineStr">
         <is>
-          <t>A 60274-2023</t>
+          <t>A 60277-2023</t>
         </is>
       </c>
       <c r="B968" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         </is>
       </c>
       <c r="G968" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -56605,7 +56605,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56655,14 +56655,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 60340-2023</t>
+          <t>A 60441-2023</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56712,14 +56712,14 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 60441-2023</t>
+          <t>A 60340-2023</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y971"/>
+  <dimension ref="A1:Y974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>45147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>43802</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>44520</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44585</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>43433</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>43860</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>43860</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44120</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>44449</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44455</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44512</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44690</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44872</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>44879</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45140</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43334</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43339</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43339</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>43348</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>43349</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43349</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>43353</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>43356</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>43358</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>43360</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>43362</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43363</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>43377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>43388</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>43390</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43393</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>43393</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>43395</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43398</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>43412</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43418</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43420</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43425</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43433</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43433</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43433</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43434</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43436</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43437</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43442</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43451</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43454</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43462</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43464</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43464</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43464</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43473</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43474</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43479</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43480</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43482</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43485</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43486</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43489</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43494</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43496</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>43501</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>43504</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>43507</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>43507</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>43507</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43510</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43510</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43524</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43530</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>43532</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>43538</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>43546</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>43556</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>43556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>43578</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>43578</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>43578</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>43585</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>43592</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43594</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>43601</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>43602</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>43605</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>43606</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>43626</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>43649</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>43653</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>43662</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>43664</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>43670</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>43676</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>43684</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>43689</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>43689</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>43690</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43692</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43700</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43700</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43705</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43705</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>43705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>43705</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43708</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43710</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43726</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43727</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43731</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43731</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43731</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43731</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43739</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>43739</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>43741</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>43745</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>43748</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>43761</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>43765</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>43770</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>43774</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>43774</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>43784</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>43784</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43786</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43787</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>43789</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43795</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>43795</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>43796</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>43796</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43798</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43800</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>43829</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>43833</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>43842</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43845</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43846</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43854</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43860</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43860</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43860</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>43861</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>43861</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>43865</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>43865</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>43867</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>43868</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>43868</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>43868</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>43872</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>43878</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>43879</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>43881</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>43886</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>43892</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>43893</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>43893</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>43894</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>43899</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>43899</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43899</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>43901</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>43901</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>43901</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>43902</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>43903</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>43916</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>43920</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>43923</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>43927</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43929</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>43963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>43966</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>43974</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>43974</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>43979</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43980</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43986</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>43992</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>44004</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>44004</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44010</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>44040</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44042</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44046</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44048</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>44048</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44054</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44055</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44060</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44060</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44062</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44068</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44074</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44075</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44082</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44084</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44088</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44089</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44090</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44105</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44116</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44120</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44125</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44137</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44138</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44145</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>44147</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44154</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44160</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>44161</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>44161</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44161</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>44161</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44161</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44164</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44165</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44173</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44175</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44179</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44180</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44181</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44182</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44195</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44195</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>44195</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44201</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44201</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44204</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44206</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44206</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44215</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44218</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44218</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44220</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44221</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>44222</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44229</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44236</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44237</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44238</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44245</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44257</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44257</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>44265</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44267</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44267</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44267</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44270</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44273</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44280</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44294</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44295</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44299</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44299</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44299</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44299</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44306</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44306</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44306</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44309</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>44312</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>44312</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>44313</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44313</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44313</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>44314</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>44319</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>44319</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>44320</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>44325</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>44333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>44334</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44336</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44349</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44351</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44354</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44354</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44368</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44368</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44371</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44391</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44391</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44393</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44393</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44403</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44404</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44412</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44417</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44418</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44419</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44421</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44439</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44441</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44442</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44443</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44447</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44447</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44448</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44448</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44453</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44455</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44460</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44462</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44464</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44466</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44469</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44470</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44474</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44474</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44474</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44474</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44477</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44477</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44477</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44480</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44488</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44488</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44488</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>44488</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>44488</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>44488</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>44488</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>44490</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>44491</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>44497</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>44497</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>44497</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44497</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44501</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44501</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44503</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>44506</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44509</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44512</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44512</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>44512</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>44512</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44512</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44512</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44512</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44512</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44514</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44515</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>44515</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>44517</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44518</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44520</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44524</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44524</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44530</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44531</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44532</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>44533</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44533</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>44533</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>44543</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44543</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44552</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44553</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44558</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44565</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44565</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44566</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44567</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>44567</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44578</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44579</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44587</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44588</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44594</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44599</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44606</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44606</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44607</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44607</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44607</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44609</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44609</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44609</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44609</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44613</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44613</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44621</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44621</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44624</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44626</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44636</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44636</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44638</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44638</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44638</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44638</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>44638</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>44641</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>44642</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44648</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44649</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44655</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>44655</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>44655</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>44656</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44656</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44656</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44657</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>44657</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>44658</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44658</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44663</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>44663</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>44663</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>44663</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>44663</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>44670</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>44670</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44672</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44672</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44674</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44677</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44678</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44678</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44679</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>44679</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>44685</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44686</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44686</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>44692</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>44697</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>44698</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44699</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>44705</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44713</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44715</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44719</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44720</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44724</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>44725</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>44726</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44733</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44735</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>44740</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>44741</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>44749</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>44750</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>44762</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>44763</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44768</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>44771</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>44771</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>44772</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44775</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>44776</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>44776</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44776</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44781</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>44790</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44796</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>44800</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>44805</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>44809</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>44809</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44809</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44810</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44810</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44812</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44817</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>44817</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>44823</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>44824</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44830</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>44831</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>44831</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44837</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>44837</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>44838</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>44838</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>44839</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44841</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>44845</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>44846</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>44854</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>44855</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>44858</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>44858</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>44859</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>44861</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>44861</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44873</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>44879</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>44880</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44880</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44881</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44881</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>44881</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>44881</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>44882</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44882</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>44882</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>44882</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>44882</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44882</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>44883</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>44887</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>44887</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>44887</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>44888</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>44893</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>44893</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>44893</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>44894</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>44894</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44895</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>44895</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>44896</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>44896</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>44908</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>44908</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>44909</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44911</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44914</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>44916</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>44916</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>44917</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>44929</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44931</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>44944</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>44945</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44945</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44945</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>44947</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44947</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>44951</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>44951</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>44959</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>44959</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>44959</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>44959</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44959</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>44961</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>44964</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>44965</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>44966</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>44967</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>44967</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44970</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44971</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>44971</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>44971</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44971</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44971</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>44977</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>44978</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>44992</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44994</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>44999</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45002</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45002</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45002</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45006</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45006</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>45006</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45007</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45008</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45008</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45009</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45015</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45021</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45022</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45033</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45033</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45035</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45037</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45038</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45038</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>45038</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45038</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45040</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>45041</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45042</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45043</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45043</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45043</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45043</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45044</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45048</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45053</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45059</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45062</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45068</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45068</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45069</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45069</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45070</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45070</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45070</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45070</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45070</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45070</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45071</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45071</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45071</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45072</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45075</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45078</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45079</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45084</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45084</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45084</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>45084</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45084</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45084</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45084</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45085</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45085</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45087</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41537,7 +41537,7 @@
         <v>45087</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45087</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45087</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45089</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45091</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45092</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45092</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45093</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45093</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42335,7 +42335,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45097</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45099</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>45104</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45104</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45104</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45112</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45114</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45120</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45124</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45132</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45132</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45133</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45134</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45134</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45134</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45134</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>45134</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45134</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45134</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45134</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45139</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45140</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45140</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45140</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45140</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45140</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45140</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45141</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45147</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>45147</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45152</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45153</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45153</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>45154</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>45154</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45157</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45157</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>45157</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45158</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45159</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45159</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45160</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45160</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45161</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45161</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45161</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45161</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45162</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45162</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45162</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45162</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45162</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45162</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45162</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45162</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45162</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45162</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45162</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45162</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45162</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45163</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45163</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45163</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>45163</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>45163</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45163</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45163</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45166</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45166</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45166</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45166</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45166</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45166</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45166</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45167</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45167</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>45167</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45167</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>45168</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45168</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45168</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45169</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>45170</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45173</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45173</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47584,7 +47584,7 @@
         <v>45173</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>45173</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>45173</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45174</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>45176</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>45176</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>45180</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45180</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>45181</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45182</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45187</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45187</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45189</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45189</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45190</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45190</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45190</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45191</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45194</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45194</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45194</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45196</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45197</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45199</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45199</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45201</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45203</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45209</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45211</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45211</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45212</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45215</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45217</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45217</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45217</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45218</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45222</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45223</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45224</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45224</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45224</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45225</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45225</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>45225</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>45225</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45225</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45225</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>45225</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>45225</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45225</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51522,7 +51522,7 @@
         <v>45226</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45227</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45227</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45227</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45227</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51807,7 +51807,7 @@
         <v>45227</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>45227</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>45230</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>45230</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52035,7 +52035,7 @@
         <v>45231</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45231</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52159,7 +52159,7 @@
         <v>45231</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52216,7 +52216,7 @@
         <v>45231</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>45231</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52323,14 +52323,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 54362-2023</t>
+          <t>A 54359-2023</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -52380,14 +52380,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 54405-2023</t>
+          <t>A 54362-2023</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52400,7 +52400,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52444,7 +52444,7 @@
         <v>45233</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52501,7 +52501,7 @@
         <v>45233</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52558,7 +52558,7 @@
         <v>45233</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52608,14 +52608,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 54359-2023</t>
+          <t>A 54575-2023</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52628,7 +52628,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>2</v>
+        <v>12.5</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52665,14 +52665,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 54577-2023</t>
+          <t>A 54405-2023</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52722,14 +52722,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 54581-2023</t>
+          <t>A 54577-2023</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52779,14 +52779,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 54575-2023</t>
+          <t>A 54581-2023</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52843,7 +52843,7 @@
         <v>45236</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52893,14 +52893,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 54904-2023</t>
+          <t>A 54909-2023</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -52950,14 +52950,14 @@
     <row r="905" ht="15" customHeight="1">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A 54914-2023</t>
+          <t>A 54915-2023</t>
         </is>
       </c>
       <c r="B905" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -53007,14 +53007,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 54909-2023</t>
+          <t>A 54904-2023</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -53064,14 +53064,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 54915-2023</t>
+          <t>A 54914-2023</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -53128,7 +53128,7 @@
         <v>45236</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53185,7 +53185,7 @@
         <v>45236</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53292,14 +53292,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 54955-2023</t>
+          <t>A 54957-2023</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53349,14 +53349,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 54957-2023</t>
+          <t>A 54955-2023</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53413,7 +53413,7 @@
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53470,7 +53470,7 @@
         <v>45237</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53520,14 +53520,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 55309-2023</t>
+          <t>A 55264-2023</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53540,7 +53540,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53577,14 +53577,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 55264-2023</t>
+          <t>A 55269-2023</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53597,7 +53597,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53634,14 +53634,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 55269-2023</t>
+          <t>A 55309-2023</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53654,7 +53654,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53691,14 +53691,14 @@
     <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>A 55765-2023</t>
+          <t>A 55763-2023</t>
         </is>
       </c>
       <c r="B918" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53748,14 +53748,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 55763-2023</t>
+          <t>A 55765-2023</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>45242</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>45242</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45243</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53976,14 +53976,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 56779-2023</t>
+          <t>A 56717-2023</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54033,14 +54033,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 56791-2023</t>
+          <t>A 56772-2023</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54090,14 +54090,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 56795-2023</t>
+          <t>A 56776-2023</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54147,14 +54147,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 56799-2023</t>
+          <t>A 56793-2023</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54204,14 +54204,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 56775-2023</t>
+          <t>A 56778-2023</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54261,14 +54261,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 56780-2023</t>
+          <t>A 56786-2023</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54318,14 +54318,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 56784-2023</t>
+          <t>A 56794-2023</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54375,14 +54375,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 56796-2023</t>
+          <t>A 56802-2023</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54432,14 +54432,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 56804-2023</t>
+          <t>A 56775-2023</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54489,14 +54489,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 56717-2023</t>
+          <t>A 56780-2023</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54546,14 +54546,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 56772-2023</t>
+          <t>A 56784-2023</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54603,14 +54603,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 56776-2023</t>
+          <t>A 56796-2023</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54660,14 +54660,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 56793-2023</t>
+          <t>A 56804-2023</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54717,14 +54717,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 56778-2023</t>
+          <t>A 56779-2023</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54737,7 +54737,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54774,14 +54774,14 @@
     <row r="937" ht="15" customHeight="1">
       <c r="A937" t="inlineStr">
         <is>
-          <t>A 56786-2023</t>
+          <t>A 56791-2023</t>
         </is>
       </c>
       <c r="B937" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
         </is>
       </c>
       <c r="G937" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="H937" t="n">
         <v>0</v>
@@ -54831,14 +54831,14 @@
     <row r="938" ht="15" customHeight="1">
       <c r="A938" t="inlineStr">
         <is>
-          <t>A 56794-2023</t>
+          <t>A 56795-2023</t>
         </is>
       </c>
       <c r="B938" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -54888,14 +54888,14 @@
     <row r="939" ht="15" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>A 56802-2023</t>
+          <t>A 56799-2023</t>
         </is>
       </c>
       <c r="B939" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -54952,7 +54952,7 @@
         <v>45245</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>45245</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55059,14 +55059,14 @@
     <row r="942" ht="15" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>A 57170-2023</t>
+          <t>A 57173-2023</t>
         </is>
       </c>
       <c r="B942" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55079,7 +55079,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -55116,14 +55116,14 @@
     <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
-          <t>A 57204-2023</t>
+          <t>A 57170-2023</t>
         </is>
       </c>
       <c r="B943" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55136,7 +55136,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -55173,14 +55173,14 @@
     <row r="944" ht="15" customHeight="1">
       <c r="A944" t="inlineStr">
         <is>
-          <t>A 57173-2023</t>
+          <t>A 57204-2023</t>
         </is>
       </c>
       <c r="B944" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -55230,14 +55230,14 @@
     <row r="945" ht="15" customHeight="1">
       <c r="A945" t="inlineStr">
         <is>
-          <t>A 58406-2023</t>
+          <t>A 57562-2023</t>
         </is>
       </c>
       <c r="B945" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         </is>
       </c>
       <c r="G945" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -55287,14 +55287,14 @@
     <row r="946" ht="15" customHeight="1">
       <c r="A946" t="inlineStr">
         <is>
-          <t>A 57562-2023</t>
+          <t>A 57571-2023</t>
         </is>
       </c>
       <c r="B946" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         </is>
       </c>
       <c r="G946" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -55344,14 +55344,14 @@
     <row r="947" ht="15" customHeight="1">
       <c r="A947" t="inlineStr">
         <is>
-          <t>A 57571-2023</t>
+          <t>A 58406-2023</t>
         </is>
       </c>
       <c r="B947" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         </is>
       </c>
       <c r="G947" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -55408,7 +55408,7 @@
         <v>45247</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55465,7 +55465,7 @@
         <v>45247</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55522,7 +55522,7 @@
         <v>45247</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55579,7 +55579,7 @@
         <v>45250</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55629,14 +55629,14 @@
     <row r="952" ht="15" customHeight="1">
       <c r="A952" t="inlineStr">
         <is>
-          <t>A 58204-2023</t>
+          <t>A 58403-2023</t>
         </is>
       </c>
       <c r="B952" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -55686,14 +55686,14 @@
     <row r="953" ht="15" customHeight="1">
       <c r="A953" t="inlineStr">
         <is>
-          <t>A 58401-2023</t>
+          <t>A 58204-2023</t>
         </is>
       </c>
       <c r="B953" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         </is>
       </c>
       <c r="G953" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -55743,14 +55743,14 @@
     <row r="954" ht="15" customHeight="1">
       <c r="A954" t="inlineStr">
         <is>
-          <t>A 58426-2023</t>
+          <t>A 58401-2023</t>
         </is>
       </c>
       <c r="B954" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -55763,7 +55763,7 @@
         </is>
       </c>
       <c r="G954" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="H954" t="n">
         <v>0</v>
@@ -55800,14 +55800,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 58403-2023</t>
+          <t>A 58426-2023</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -55820,7 +55820,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -55864,7 +55864,7 @@
         <v>45252</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -55914,14 +55914,14 @@
     <row r="957" ht="15" customHeight="1">
       <c r="A957" t="inlineStr">
         <is>
-          <t>A 59075-2023</t>
+          <t>A 59036-2023</t>
         </is>
       </c>
       <c r="B957" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -55934,7 +55934,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="H957" t="n">
         <v>0</v>
@@ -55971,14 +55971,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 59036-2023</t>
+          <t>A 59075-2023</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -55991,7 +55991,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56035,7 +56035,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56085,14 +56085,14 @@
     <row r="960" ht="15" customHeight="1">
       <c r="A960" t="inlineStr">
         <is>
-          <t>A 59802-2023</t>
+          <t>A 59991-2023</t>
         </is>
       </c>
       <c r="B960" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         </is>
       </c>
       <c r="G960" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H960" t="n">
         <v>0</v>
@@ -56142,14 +56142,14 @@
     <row r="961" ht="15" customHeight="1">
       <c r="A961" t="inlineStr">
         <is>
-          <t>A 59990-2023</t>
+          <t>A 59802-2023</t>
         </is>
       </c>
       <c r="B961" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56162,7 +56162,7 @@
         </is>
       </c>
       <c r="G961" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H961" t="n">
         <v>0</v>
@@ -56199,14 +56199,14 @@
     <row r="962" ht="15" customHeight="1">
       <c r="A962" t="inlineStr">
         <is>
-          <t>A 59991-2023</t>
+          <t>A 59990-2023</t>
         </is>
       </c>
       <c r="B962" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         </is>
       </c>
       <c r="G962" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -56256,14 +56256,14 @@
     <row r="963" ht="15" customHeight="1">
       <c r="A963" t="inlineStr">
         <is>
-          <t>A 60084-2023</t>
+          <t>A 60016-2023</t>
         </is>
       </c>
       <c r="B963" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56276,7 +56276,7 @@
         </is>
       </c>
       <c r="G963" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="H963" t="n">
         <v>0</v>
@@ -56313,14 +56313,14 @@
     <row r="964" ht="15" customHeight="1">
       <c r="A964" t="inlineStr">
         <is>
-          <t>A 60016-2023</t>
+          <t>A 60084-2023</t>
         </is>
       </c>
       <c r="B964" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         </is>
       </c>
       <c r="G964" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="H964" t="n">
         <v>0</v>
@@ -56370,14 +56370,14 @@
     <row r="965" ht="15" customHeight="1">
       <c r="A965" t="inlineStr">
         <is>
-          <t>A 60293-2023</t>
+          <t>A 60274-2023</t>
         </is>
       </c>
       <c r="B965" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         </is>
       </c>
       <c r="G965" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -56427,14 +56427,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 60274-2023</t>
+          <t>A 60293-2023</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -56484,14 +56484,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 60290-2023</t>
+          <t>A 60277-2023</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56541,14 +56541,14 @@
     <row r="968" ht="15" customHeight="1">
       <c r="A968" t="inlineStr">
         <is>
-          <t>A 60277-2023</t>
+          <t>A 60291-2023</t>
         </is>
       </c>
       <c r="B968" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         </is>
       </c>
       <c r="G968" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -56598,14 +56598,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 60291-2023</t>
+          <t>A 60290-2023</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -56662,7 +56662,7 @@
         <v>45259</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56709,7 +56709,7 @@
       </c>
       <c r="R970" s="2" t="inlineStr"/>
     </row>
-    <row r="971">
+    <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
           <t>A 60340-2023</t>
@@ -56719,7 +56719,7 @@
         <v>45259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56765,6 +56765,177 @@
         <v>0</v>
       </c>
       <c r="R971" s="2" t="inlineStr"/>
+    </row>
+    <row r="972" ht="15" customHeight="1">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>A 60986-2023</t>
+        </is>
+      </c>
+      <c r="B972" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C972" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G972" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H972" t="n">
+        <v>0</v>
+      </c>
+      <c r="I972" t="n">
+        <v>0</v>
+      </c>
+      <c r="J972" t="n">
+        <v>0</v>
+      </c>
+      <c r="K972" t="n">
+        <v>0</v>
+      </c>
+      <c r="L972" t="n">
+        <v>0</v>
+      </c>
+      <c r="M972" t="n">
+        <v>0</v>
+      </c>
+      <c r="N972" t="n">
+        <v>0</v>
+      </c>
+      <c r="O972" t="n">
+        <v>0</v>
+      </c>
+      <c r="P972" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q972" t="n">
+        <v>0</v>
+      </c>
+      <c r="R972" s="2" t="inlineStr"/>
+    </row>
+    <row r="973" ht="15" customHeight="1">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>A 61039-2023</t>
+        </is>
+      </c>
+      <c r="B973" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C973" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G973" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H973" t="n">
+        <v>0</v>
+      </c>
+      <c r="I973" t="n">
+        <v>0</v>
+      </c>
+      <c r="J973" t="n">
+        <v>0</v>
+      </c>
+      <c r="K973" t="n">
+        <v>0</v>
+      </c>
+      <c r="L973" t="n">
+        <v>0</v>
+      </c>
+      <c r="M973" t="n">
+        <v>0</v>
+      </c>
+      <c r="N973" t="n">
+        <v>0</v>
+      </c>
+      <c r="O973" t="n">
+        <v>0</v>
+      </c>
+      <c r="P973" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q973" t="n">
+        <v>0</v>
+      </c>
+      <c r="R973" s="2" t="inlineStr"/>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>A 60912-2023</t>
+        </is>
+      </c>
+      <c r="B974" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C974" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G974" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H974" t="n">
+        <v>0</v>
+      </c>
+      <c r="I974" t="n">
+        <v>0</v>
+      </c>
+      <c r="J974" t="n">
+        <v>0</v>
+      </c>
+      <c r="K974" t="n">
+        <v>0</v>
+      </c>
+      <c r="L974" t="n">
+        <v>0</v>
+      </c>
+      <c r="M974" t="n">
+        <v>0</v>
+      </c>
+      <c r="N974" t="n">
+        <v>0</v>
+      </c>
+      <c r="O974" t="n">
+        <v>0</v>
+      </c>
+      <c r="P974" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q974" t="n">
+        <v>0</v>
+      </c>
+      <c r="R974" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -564,7 +564,7 @@
         <v>45147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>43802</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>44520</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44585</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>43433</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>43860</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>43860</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44120</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>44449</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44455</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44512</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44690</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44872</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>44879</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45140</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43334</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43339</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43339</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>43348</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>43349</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43349</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>43353</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>43356</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>43358</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>43360</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>43362</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43363</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>43377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>43388</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>43390</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43393</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>43393</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>43395</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43398</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>43412</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43418</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43420</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43425</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43433</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43433</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43433</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43434</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43436</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43437</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43442</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43451</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43454</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43462</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43464</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43464</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43464</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43473</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43474</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43479</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43480</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43482</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43485</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43486</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43489</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43494</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43496</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>43501</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>43504</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>43507</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>43507</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>43507</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43510</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43510</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43524</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43530</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>43532</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>43538</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>43546</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>43556</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>43556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>43578</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>43578</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>43578</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>43585</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>43592</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43594</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>43601</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>43602</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>43605</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>43606</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>43626</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>43649</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>43653</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>43662</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>43664</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>43670</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>43676</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>43684</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>43689</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>43689</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>43690</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43692</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43700</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43700</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43705</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43705</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>43705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>43705</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43708</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43710</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43726</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43727</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43731</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43731</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43731</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43731</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43739</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>43739</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>43741</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>43745</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>43748</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>43761</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>43765</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>43770</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>43774</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>43774</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>43784</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>43784</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43786</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43787</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>43789</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43795</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>43795</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>43796</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>43796</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43798</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43800</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>43829</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>43833</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>43842</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43845</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43846</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43854</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43860</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43860</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43860</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>43861</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>43861</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>43865</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>43865</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>43867</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>43868</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>43868</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>43868</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>43872</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>43878</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>43879</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>43881</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>43886</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>43892</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>43893</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>43893</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>43894</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>43899</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>43899</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43899</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>43901</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>43901</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>43901</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>43902</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>43903</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>43916</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>43920</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>43923</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>43927</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43929</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>43963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>43966</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>43974</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>43974</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>43979</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43980</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43986</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>43992</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>44004</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>44004</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44010</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>44040</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44042</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44046</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44048</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>44048</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44054</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44055</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44060</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44060</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44062</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44068</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44074</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44075</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44082</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44084</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44088</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44089</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44090</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44105</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44116</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44120</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44125</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44137</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44138</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44145</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>44147</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44154</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44160</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>44161</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>44161</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44161</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>44161</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44161</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44164</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44165</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44173</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44175</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44179</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44180</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44181</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44182</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44195</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44195</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>44195</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44201</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44201</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44204</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44206</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44206</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44215</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44218</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44218</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44220</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44221</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>44222</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44229</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44236</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44237</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44238</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44245</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44257</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44257</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>44265</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44267</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44267</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44267</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44270</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44273</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44280</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44294</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44295</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44299</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44299</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44299</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44299</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44306</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44306</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44306</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44309</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>44312</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>44312</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>44313</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44313</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44313</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>44314</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>44319</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>44319</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>44320</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>44325</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>44333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>44334</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44336</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44349</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44351</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44354</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44354</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44368</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44368</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44371</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44391</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44391</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44393</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44393</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44403</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44404</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44412</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44417</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44418</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44419</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44421</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44439</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44441</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44442</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44443</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44447</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44447</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44448</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44448</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44453</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44455</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44460</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44462</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44464</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44466</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44469</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44470</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44474</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44474</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44474</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44474</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44477</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44477</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44477</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44480</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44488</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44488</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44488</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>44488</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>44488</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>44488</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>44488</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>44490</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>44491</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>44497</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>44497</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>44497</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44497</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44501</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44501</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44503</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>44506</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44509</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44512</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44512</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>44512</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>44512</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44512</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44512</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44512</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44512</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44514</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44515</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>44515</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>44517</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44518</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44520</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44524</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44524</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44530</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44531</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44532</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>44533</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44533</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>44533</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>44543</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44543</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44552</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44553</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44558</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44565</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44565</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44566</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44567</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>44567</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44578</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44579</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44587</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44588</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44594</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44599</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44606</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44606</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44607</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44607</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44607</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44609</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44609</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44609</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44609</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44613</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44613</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44621</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44621</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44624</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44626</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44636</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44636</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44638</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44638</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44638</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44638</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>44638</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>44641</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>44642</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44648</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44649</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44655</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>44655</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>44655</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>44656</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44656</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44656</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44657</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>44657</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>44658</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44658</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44663</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>44663</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>44663</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>44663</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>44663</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>44670</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>44670</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44672</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44672</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44674</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44677</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44678</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44678</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44679</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>44679</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>44685</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44686</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44686</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>44692</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>44697</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>44698</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44699</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>44705</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44713</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44715</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44719</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44720</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44724</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>44725</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>44726</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44733</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44735</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>44740</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>44741</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>44749</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>44750</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>44762</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>44763</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44768</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>44771</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>44771</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>44772</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44775</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>44776</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>44776</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44776</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44781</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>44790</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44796</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>44800</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>44805</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>44809</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>44809</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44809</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44810</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44810</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44812</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44817</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>44817</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>44823</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>44824</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44830</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>44831</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>44831</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44837</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>44837</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>44838</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>44838</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>44839</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44841</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>44845</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>44846</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>44854</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>44855</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>44858</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>44858</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>44859</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>44861</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>44861</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44873</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>44879</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>44880</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44880</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44881</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44881</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>44881</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>44881</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>44882</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44882</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>44882</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>44882</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>44882</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44882</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>44883</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>44887</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>44887</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>44887</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>44888</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>44893</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>44893</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>44893</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>44894</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>44894</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44895</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>44895</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>44896</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>44896</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>44908</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>44908</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>44909</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44911</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44914</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>44916</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>44916</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>44917</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>44929</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44931</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>44944</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>44945</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44945</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44945</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>44947</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44947</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>44951</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>44951</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>44959</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>44959</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>44959</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>44959</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44959</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>44961</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>44964</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>44965</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>44966</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>44967</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>44967</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44970</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44971</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>44971</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>44971</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44971</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44971</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>44977</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>44978</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>44992</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44994</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>44999</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45002</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45002</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45002</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45006</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45006</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>45006</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45007</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45008</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45008</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45009</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45015</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45021</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45022</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45033</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45033</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45035</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45037</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45038</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45038</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>45038</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45038</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45040</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>45041</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45042</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45043</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45043</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45043</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45043</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45044</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45048</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45053</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45059</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45062</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45068</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45068</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45069</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45069</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45070</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45070</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45070</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45070</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45070</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45070</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45071</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45071</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45071</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45072</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45075</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45078</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45079</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45084</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45084</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45084</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>45084</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45084</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45084</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45084</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45085</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45085</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45087</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41537,7 +41537,7 @@
         <v>45087</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45087</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45087</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45089</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45091</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45092</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45092</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45093</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45093</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42335,7 +42335,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45097</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45099</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>45104</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45104</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45104</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45112</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45114</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45120</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45124</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45132</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45132</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45133</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45134</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45134</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45134</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45134</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>45134</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45134</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45134</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45134</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45139</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45140</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45140</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45140</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45140</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45140</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45140</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45141</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45147</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>45147</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45152</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45153</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45153</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>45154</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>45154</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45157</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45157</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>45157</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45158</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45159</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45159</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45160</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45160</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45161</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45161</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45161</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45161</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45162</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45162</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45162</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45162</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45162</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45162</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45162</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45162</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45162</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45162</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45162</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45162</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45162</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45163</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45163</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45163</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>45163</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>45163</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45163</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45163</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45166</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45166</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45166</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45166</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45166</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45166</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45166</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45167</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45167</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>45167</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45167</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>45168</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45168</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45168</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45169</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>45170</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45173</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45173</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47584,7 +47584,7 @@
         <v>45173</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>45173</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>45173</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45174</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>45176</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>45176</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>45180</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45180</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>45181</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45182</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45187</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45187</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45189</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45189</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45190</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45190</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45190</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45191</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45194</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45194</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45194</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45196</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45197</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45199</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45199</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45201</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45203</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45209</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45211</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45211</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45212</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45215</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45217</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45217</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45217</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45218</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45222</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45223</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45224</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45224</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45224</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45225</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45225</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>45225</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>45225</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45225</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45225</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>45225</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>45225</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45225</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51522,7 +51522,7 @@
         <v>45226</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45227</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45227</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45227</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45227</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51807,7 +51807,7 @@
         <v>45227</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>45227</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>45230</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>45230</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52035,7 +52035,7 @@
         <v>45231</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45231</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52159,7 +52159,7 @@
         <v>45231</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52216,7 +52216,7 @@
         <v>45231</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>45231</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52323,14 +52323,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 54359-2023</t>
+          <t>A 54581-2023</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -52380,14 +52380,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 54362-2023</t>
+          <t>A 54577-2023</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52400,7 +52400,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52437,14 +52437,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 54389-2023</t>
+          <t>A 54575-2023</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>1.8</v>
+        <v>12.5</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52494,14 +52494,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 54403-2023</t>
+          <t>A 54405-2023</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52551,14 +52551,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 54407-2023</t>
+          <t>A 54362-2023</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52608,14 +52608,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 54575-2023</t>
+          <t>A 54359-2023</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52628,7 +52628,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>12.5</v>
+        <v>2</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52665,14 +52665,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 54405-2023</t>
+          <t>A 54407-2023</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52722,14 +52722,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 54577-2023</t>
+          <t>A 54403-2023</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52779,14 +52779,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 54581-2023</t>
+          <t>A 54389-2023</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52843,7 +52843,7 @@
         <v>45236</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52893,14 +52893,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 54909-2023</t>
+          <t>A 54904-2023</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -52950,14 +52950,14 @@
     <row r="905" ht="15" customHeight="1">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A 54915-2023</t>
+          <t>A 54914-2023</t>
         </is>
       </c>
       <c r="B905" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -53007,14 +53007,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 54904-2023</t>
+          <t>A 54906-2023</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -53064,14 +53064,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 54914-2023</t>
+          <t>A 54912-2023</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -53121,14 +53121,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 54906-2023</t>
+          <t>A 54909-2023</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         </is>
       </c>
       <c r="G908" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -53178,14 +53178,14 @@
     <row r="909" ht="15" customHeight="1">
       <c r="A909" t="inlineStr">
         <is>
-          <t>A 54912-2023</t>
+          <t>A 54915-2023</t>
         </is>
       </c>
       <c r="B909" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         </is>
       </c>
       <c r="G909" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="H909" t="n">
         <v>0</v>
@@ -53235,14 +53235,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 54903-2023</t>
+          <t>A 54955-2023</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53292,14 +53292,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 54957-2023</t>
+          <t>A 54903-2023</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>2.9</v>
+        <v>6.4</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53349,14 +53349,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 54955-2023</t>
+          <t>A 54957-2023</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53406,14 +53406,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 55267-2023</t>
+          <t>A 55160-2023</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -53463,14 +53463,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 55160-2023</t>
+          <t>A 55264-2023</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -53520,14 +53520,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 55264-2023</t>
+          <t>A 55269-2023</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53540,7 +53540,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53577,14 +53577,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 55269-2023</t>
+          <t>A 55267-2023</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53597,7 +53597,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53641,7 +53641,7 @@
         <v>45237</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53698,7 +53698,7 @@
         <v>45239</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>45239</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>45242</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>45242</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45243</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53976,14 +53976,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 56717-2023</t>
+          <t>A 56778-2023</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -54033,14 +54033,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 56772-2023</t>
+          <t>A 56786-2023</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54090,14 +54090,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 56776-2023</t>
+          <t>A 56794-2023</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54147,14 +54147,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 56793-2023</t>
+          <t>A 56802-2023</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54204,14 +54204,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 56778-2023</t>
+          <t>A 56717-2023</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54261,14 +54261,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 56786-2023</t>
+          <t>A 56772-2023</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54318,14 +54318,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 56794-2023</t>
+          <t>A 56776-2023</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54375,14 +54375,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 56802-2023</t>
+          <t>A 56793-2023</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54432,14 +54432,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 56775-2023</t>
+          <t>A 56779-2023</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54489,14 +54489,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 56780-2023</t>
+          <t>A 56791-2023</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54546,14 +54546,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 56784-2023</t>
+          <t>A 56795-2023</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54603,14 +54603,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 56796-2023</t>
+          <t>A 56799-2023</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54660,14 +54660,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 56804-2023</t>
+          <t>A 56775-2023</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54717,14 +54717,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 56779-2023</t>
+          <t>A 56780-2023</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54737,7 +54737,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54774,14 +54774,14 @@
     <row r="937" ht="15" customHeight="1">
       <c r="A937" t="inlineStr">
         <is>
-          <t>A 56791-2023</t>
+          <t>A 56784-2023</t>
         </is>
       </c>
       <c r="B937" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
         </is>
       </c>
       <c r="G937" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H937" t="n">
         <v>0</v>
@@ -54831,14 +54831,14 @@
     <row r="938" ht="15" customHeight="1">
       <c r="A938" t="inlineStr">
         <is>
-          <t>A 56795-2023</t>
+          <t>A 56796-2023</t>
         </is>
       </c>
       <c r="B938" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         </is>
       </c>
       <c r="G938" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H938" t="n">
         <v>0</v>
@@ -54888,14 +54888,14 @@
     <row r="939" ht="15" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>A 56799-2023</t>
+          <t>A 56804-2023</t>
         </is>
       </c>
       <c r="B939" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -54945,14 +54945,14 @@
     <row r="940" ht="15" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>A 57215-2023</t>
+          <t>A 57196-2023</t>
         </is>
       </c>
       <c r="B940" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -55002,14 +55002,14 @@
     <row r="941" ht="15" customHeight="1">
       <c r="A941" t="inlineStr">
         <is>
-          <t>A 57196-2023</t>
+          <t>A 57173-2023</t>
         </is>
       </c>
       <c r="B941" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="H941" t="n">
         <v>0</v>
@@ -55059,14 +55059,14 @@
     <row r="942" ht="15" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>A 57173-2023</t>
+          <t>A 57170-2023</t>
         </is>
       </c>
       <c r="B942" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55079,7 +55079,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -55116,14 +55116,14 @@
     <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
-          <t>A 57170-2023</t>
+          <t>A 57204-2023</t>
         </is>
       </c>
       <c r="B943" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55136,7 +55136,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -55173,14 +55173,14 @@
     <row r="944" ht="15" customHeight="1">
       <c r="A944" t="inlineStr">
         <is>
-          <t>A 57204-2023</t>
+          <t>A 57215-2023</t>
         </is>
       </c>
       <c r="B944" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -55237,7 +55237,7 @@
         <v>45246</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55294,7 +55294,7 @@
         <v>45246</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55351,7 +55351,7 @@
         <v>45246</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55401,14 +55401,14 @@
     <row r="948" ht="15" customHeight="1">
       <c r="A948" t="inlineStr">
         <is>
-          <t>A 57854-2023</t>
+          <t>A 57917-2023</t>
         </is>
       </c>
       <c r="B948" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -55458,14 +55458,14 @@
     <row r="949" ht="15" customHeight="1">
       <c r="A949" t="inlineStr">
         <is>
-          <t>A 57916-2023</t>
+          <t>A 57854-2023</t>
         </is>
       </c>
       <c r="B949" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -55515,14 +55515,14 @@
     <row r="950" ht="15" customHeight="1">
       <c r="A950" t="inlineStr">
         <is>
-          <t>A 57917-2023</t>
+          <t>A 57916-2023</t>
         </is>
       </c>
       <c r="B950" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         </is>
       </c>
       <c r="G950" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="H950" t="n">
         <v>0</v>
@@ -55579,7 +55579,7 @@
         <v>45250</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55636,7 +55636,7 @@
         <v>45250</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45250</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55750,7 +55750,7 @@
         <v>45250</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>45250</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -55864,7 +55864,7 @@
         <v>45252</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45252</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>45252</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56035,7 +56035,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56085,14 +56085,14 @@
     <row r="960" ht="15" customHeight="1">
       <c r="A960" t="inlineStr">
         <is>
-          <t>A 59991-2023</t>
+          <t>A 59802-2023</t>
         </is>
       </c>
       <c r="B960" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         </is>
       </c>
       <c r="G960" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="H960" t="n">
         <v>0</v>
@@ -56142,14 +56142,14 @@
     <row r="961" ht="15" customHeight="1">
       <c r="A961" t="inlineStr">
         <is>
-          <t>A 59802-2023</t>
+          <t>A 59991-2023</t>
         </is>
       </c>
       <c r="B961" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56162,7 +56162,7 @@
         </is>
       </c>
       <c r="G961" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H961" t="n">
         <v>0</v>
@@ -56206,7 +56206,7 @@
         <v>45257</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56263,7 +56263,7 @@
         <v>45258</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56313,14 +56313,14 @@
     <row r="964" ht="15" customHeight="1">
       <c r="A964" t="inlineStr">
         <is>
-          <t>A 60084-2023</t>
+          <t>A 60277-2023</t>
         </is>
       </c>
       <c r="B964" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         </is>
       </c>
       <c r="G964" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="H964" t="n">
         <v>0</v>
@@ -56370,14 +56370,14 @@
     <row r="965" ht="15" customHeight="1">
       <c r="A965" t="inlineStr">
         <is>
-          <t>A 60274-2023</t>
+          <t>A 60291-2023</t>
         </is>
       </c>
       <c r="B965" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         </is>
       </c>
       <c r="G965" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -56427,14 +56427,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 60293-2023</t>
+          <t>A 60274-2023</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -56484,14 +56484,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 60277-2023</t>
+          <t>A 60084-2023</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56541,14 +56541,14 @@
     <row r="968" ht="15" customHeight="1">
       <c r="A968" t="inlineStr">
         <is>
-          <t>A 60291-2023</t>
+          <t>A 60293-2023</t>
         </is>
       </c>
       <c r="B968" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         </is>
       </c>
       <c r="G968" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -56605,7 +56605,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56655,14 +56655,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 60441-2023</t>
+          <t>A 60340-2023</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56712,14 +56712,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 60340-2023</t>
+          <t>A 60441-2023</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -56769,14 +56769,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 60986-2023</t>
+          <t>A 61039-2023</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -56826,14 +56826,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 61039-2023</t>
+          <t>A 60986-2023</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -56890,7 +56890,7 @@
         <v>45261</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -564,7 +564,7 @@
         <v>45147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>43802</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>44520</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44585</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>43433</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>43860</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>43860</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44120</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>44449</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44455</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44512</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44690</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44872</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>44879</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45140</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43334</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43339</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43339</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>43346</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>43348</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>43349</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43349</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>43353</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>43356</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>43358</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>43360</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>43362</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43363</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>43377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>43388</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>43390</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43393</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>43393</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>43395</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43398</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>43412</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43418</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43420</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43425</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43433</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43433</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43433</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43434</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43436</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43437</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43442</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43451</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43454</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43462</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43464</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43464</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43464</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43473</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43474</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43479</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43480</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43482</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43485</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43486</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43489</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43494</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43496</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>43501</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>43504</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>43507</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>43507</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>43507</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43510</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43510</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43524</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43530</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>43532</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>43538</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>43546</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>43556</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>43556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>43578</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>43578</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>43578</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>43585</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>43592</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43594</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>43601</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>43602</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>43605</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>43606</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>43626</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>43649</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>43653</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>43662</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>43664</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>43670</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>43676</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>43684</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>43689</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>43689</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>43690</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>43692</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>43700</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43700</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>43704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>43705</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43705</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>43705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>43705</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43708</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43710</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43726</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43727</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43731</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43731</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>43731</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>43731</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43739</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>43739</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>43741</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>43745</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>43748</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>43761</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>43765</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>43770</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>43774</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>43774</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>43784</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>43784</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43786</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43787</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>43789</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43795</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>43795</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>43796</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>43796</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43798</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>43800</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>43829</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>43833</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>43842</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43845</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43846</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43854</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43860</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43860</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>43860</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>43861</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>43861</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>43865</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>43865</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>43867</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>43868</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>43868</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>43868</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>43872</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>43878</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>43879</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>43881</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>43886</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>43892</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>43893</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>43893</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>43894</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>43899</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>43899</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43899</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>43901</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>43901</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>43901</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>43902</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>43903</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>43916</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>43920</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>43923</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>43927</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>43929</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>43963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>43966</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>43974</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>43974</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>43979</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43980</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43986</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>43992</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>44004</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>44004</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44010</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>44040</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44042</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44046</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44048</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>44048</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44054</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44055</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44060</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44060</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44062</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44068</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44074</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44075</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44082</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44084</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44088</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44089</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44090</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44105</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>44116</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44120</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44125</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44137</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44138</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44145</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>44147</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44154</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44160</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>44161</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>44161</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44161</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>44161</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44161</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44164</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44165</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44173</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44175</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44179</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44180</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44181</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44182</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44195</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44195</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>44195</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44201</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44201</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44204</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44206</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44206</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44215</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44218</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44218</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44220</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44221</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>44222</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44229</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44236</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44237</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44238</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44245</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44257</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44257</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>44265</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44267</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>44267</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44267</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44270</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44273</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44280</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44294</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44295</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44299</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44299</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44299</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44299</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44306</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44306</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44306</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44309</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>44312</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>44312</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>44313</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44313</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44313</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>44314</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>44319</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>44319</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>44320</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>44325</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>44333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>44334</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44336</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44349</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44351</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44354</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44354</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44368</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44368</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44371</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44391</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44391</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44393</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44393</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44403</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44404</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44412</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44417</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44418</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44419</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44421</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44439</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44441</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44442</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44443</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44447</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44447</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44448</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44448</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44453</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44455</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44460</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44462</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44464</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44466</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44469</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44470</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44474</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44474</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44474</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44474</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44477</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44477</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44477</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44480</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44488</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44488</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44488</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>44488</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>44488</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>44488</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>44488</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>44490</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>44491</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>44497</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>44497</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>44497</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44497</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44501</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44501</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44503</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>44506</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44509</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44512</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44512</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>44512</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>44512</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44512</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44512</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44512</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44512</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44514</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44515</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>44515</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>44517</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44518</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44520</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44524</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44524</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44530</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44531</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44532</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>44533</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44533</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>44533</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>44543</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44543</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44552</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44553</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44558</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44565</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44565</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44566</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44567</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>44567</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44578</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44579</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44587</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44588</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44594</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44599</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44606</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44606</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44607</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44607</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44607</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44609</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44609</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44609</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44609</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44613</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44613</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44621</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44621</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44624</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44626</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44636</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44636</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44638</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44638</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44638</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>44638</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>44638</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>44641</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>44642</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44648</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44649</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44655</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>44655</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>44655</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>44656</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44656</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44656</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44657</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>44657</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>44658</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44658</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44663</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>44663</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>44663</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>44663</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>44663</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>44670</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>44670</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44672</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44672</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44674</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44677</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44678</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44678</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44679</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>44679</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>44685</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44686</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44686</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>44692</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>44697</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>44698</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44699</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>44705</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44713</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44715</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44719</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44720</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44724</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>44725</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>44726</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44733</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44735</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>44740</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>44741</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>44749</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>44750</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>44760</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>44762</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>44763</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44768</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>44771</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>44771</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>44772</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44775</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>44776</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>44776</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44776</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44781</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>44790</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44796</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>44800</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>44805</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>44809</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>44809</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44809</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44810</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44810</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44812</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44817</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>44817</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>44823</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>44824</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44830</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>44831</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>44831</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44837</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>44837</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>44838</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>44838</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>44839</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44841</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>44845</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>44846</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44847</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>44854</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>44855</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>44858</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>44858</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>44859</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>44861</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>44861</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44868</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>44869</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44873</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>44879</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>44880</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44880</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44881</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44881</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>44881</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>44881</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>44882</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44882</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>44882</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>44882</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>44882</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44882</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>44883</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>44887</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>44887</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>44887</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>44888</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>44893</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>44893</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>44893</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>44894</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>44894</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44895</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>44895</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>44896</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>44896</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>44908</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>44908</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>44909</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44911</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44914</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>44916</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>44916</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>44917</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>44929</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44931</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>44944</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>44945</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44945</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44945</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>44947</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44947</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>44951</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>44951</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>44959</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>44959</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>44959</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>44959</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44959</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>44961</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>44964</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>44965</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>44966</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>44967</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>44967</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44970</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44971</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>44971</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>44971</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44971</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44971</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>44977</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>44978</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>44992</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44994</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>44999</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45002</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45002</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45002</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45006</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45006</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>45006</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45007</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45008</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45008</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45009</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45015</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45021</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45022</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45033</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45033</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45035</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45037</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45038</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45038</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>45038</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45038</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45040</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>45041</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45042</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45043</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45043</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45043</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45043</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45044</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45048</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45053</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45059</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45062</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45068</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45068</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45069</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45069</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45070</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45070</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45070</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45070</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45070</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45070</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45071</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45071</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45071</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45072</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45075</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45078</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45079</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45084</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45084</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45084</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>45084</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45084</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45084</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45084</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45085</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45085</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45087</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41537,7 +41537,7 @@
         <v>45087</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45087</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45087</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45089</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45090</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45091</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45092</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45092</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45093</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45093</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42335,7 +42335,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45096</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45097</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45098</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45099</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>45104</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45104</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45104</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45112</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45114</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45120</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45124</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45132</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45132</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45133</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45134</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45134</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45134</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45134</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>45134</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45134</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45134</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45134</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45139</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45140</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45140</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45140</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45140</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45140</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45140</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45141</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45147</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>45147</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45152</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45153</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45153</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>45154</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>45154</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45157</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45157</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>45157</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45158</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45159</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45159</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45160</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45160</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45161</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45161</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45161</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45161</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45162</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45162</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45162</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45162</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45162</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45162</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45162</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45162</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45162</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45162</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45162</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45162</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45162</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45163</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45163</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45163</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>45163</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>45163</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45163</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45163</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45166</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45166</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45166</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45166</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45166</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45166</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45166</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45167</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45167</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>45167</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45167</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>45168</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45168</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45168</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45169</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>45170</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45173</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45173</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47584,7 +47584,7 @@
         <v>45173</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>45173</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>45173</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45174</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>45176</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>45176</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>45180</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45180</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>45181</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45182</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45187</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45187</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45189</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45189</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45190</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45190</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45190</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45191</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45194</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45194</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45194</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45196</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45197</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45199</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45199</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45201</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45203</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45209</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45211</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45211</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45212</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45215</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45217</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45217</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45217</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45218</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45222</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45223</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45224</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45224</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45224</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45225</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45225</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>45225</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>45225</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45225</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45225</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>45225</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>45225</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45225</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51522,7 +51522,7 @@
         <v>45226</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45227</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45227</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45227</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45227</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51807,7 +51807,7 @@
         <v>45227</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>45227</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>45230</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>45230</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52035,7 +52035,7 @@
         <v>45231</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>45231</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52159,7 +52159,7 @@
         <v>45231</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52216,7 +52216,7 @@
         <v>45231</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>45231</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>45233</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>45233</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>45233</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52501,7 +52501,7 @@
         <v>45233</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52558,7 +52558,7 @@
         <v>45233</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52615,7 +52615,7 @@
         <v>45233</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52672,7 +52672,7 @@
         <v>45233</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>45233</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>45233</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52836,14 +52836,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 54699-2023</t>
+          <t>A 54906-2023</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52856,7 +52856,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -52893,14 +52893,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 54904-2023</t>
+          <t>A 54912-2023</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -52950,14 +52950,14 @@
     <row r="905" ht="15" customHeight="1">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A 54914-2023</t>
+          <t>A 54699-2023</t>
         </is>
       </c>
       <c r="B905" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -53007,14 +53007,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 54906-2023</t>
+          <t>A 54909-2023</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -53064,14 +53064,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 54912-2023</t>
+          <t>A 54915-2023</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -53121,14 +53121,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 54909-2023</t>
+          <t>A 54955-2023</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         </is>
       </c>
       <c r="G908" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -53178,14 +53178,14 @@
     <row r="909" ht="15" customHeight="1">
       <c r="A909" t="inlineStr">
         <is>
-          <t>A 54915-2023</t>
+          <t>A 54904-2023</t>
         </is>
       </c>
       <c r="B909" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         </is>
       </c>
       <c r="G909" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="H909" t="n">
         <v>0</v>
@@ -53235,14 +53235,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 54955-2023</t>
+          <t>A 54914-2023</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53299,7 +53299,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53356,7 +53356,7 @@
         <v>45236</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53413,7 +53413,7 @@
         <v>45237</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53470,7 +53470,7 @@
         <v>45237</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>45237</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45237</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53641,7 +53641,7 @@
         <v>45237</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53698,7 +53698,7 @@
         <v>45239</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>45239</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>45242</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>45242</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45243</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>45244</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54097,7 +54097,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54204,14 +54204,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 56717-2023</t>
+          <t>A 56779-2023</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54261,14 +54261,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 56772-2023</t>
+          <t>A 56791-2023</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54318,14 +54318,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 56776-2023</t>
+          <t>A 56795-2023</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54375,14 +54375,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 56793-2023</t>
+          <t>A 56799-2023</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54432,14 +54432,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 56779-2023</t>
+          <t>A 56775-2023</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54489,14 +54489,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 56791-2023</t>
+          <t>A 56780-2023</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54546,14 +54546,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 56795-2023</t>
+          <t>A 56784-2023</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54603,14 +54603,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 56799-2023</t>
+          <t>A 56796-2023</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54660,14 +54660,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 56775-2023</t>
+          <t>A 56804-2023</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54717,14 +54717,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 56780-2023</t>
+          <t>A 56717-2023</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54774,14 +54774,14 @@
     <row r="937" ht="15" customHeight="1">
       <c r="A937" t="inlineStr">
         <is>
-          <t>A 56784-2023</t>
+          <t>A 56772-2023</t>
         </is>
       </c>
       <c r="B937" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
         </is>
       </c>
       <c r="G937" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H937" t="n">
         <v>0</v>
@@ -54831,14 +54831,14 @@
     <row r="938" ht="15" customHeight="1">
       <c r="A938" t="inlineStr">
         <is>
-          <t>A 56796-2023</t>
+          <t>A 56776-2023</t>
         </is>
       </c>
       <c r="B938" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         </is>
       </c>
       <c r="G938" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="H938" t="n">
         <v>0</v>
@@ -54888,14 +54888,14 @@
     <row r="939" ht="15" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>A 56804-2023</t>
+          <t>A 56793-2023</t>
         </is>
       </c>
       <c r="B939" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -54945,14 +54945,14 @@
     <row r="940" ht="15" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>A 57196-2023</t>
+          <t>A 57170-2023</t>
         </is>
       </c>
       <c r="B940" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55002,14 +55002,14 @@
     <row r="941" ht="15" customHeight="1">
       <c r="A941" t="inlineStr">
         <is>
-          <t>A 57173-2023</t>
+          <t>A 57196-2023</t>
         </is>
       </c>
       <c r="B941" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="H941" t="n">
         <v>0</v>
@@ -55059,14 +55059,14 @@
     <row r="942" ht="15" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>A 57170-2023</t>
+          <t>A 57173-2023</t>
         </is>
       </c>
       <c r="B942" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55079,7 +55079,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -55123,7 +55123,7 @@
         <v>45245</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55180,7 +55180,7 @@
         <v>45245</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55237,7 +55237,7 @@
         <v>45246</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55294,7 +55294,7 @@
         <v>45246</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55351,7 +55351,7 @@
         <v>45246</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55401,14 +55401,14 @@
     <row r="948" ht="15" customHeight="1">
       <c r="A948" t="inlineStr">
         <is>
-          <t>A 57917-2023</t>
+          <t>A 57854-2023</t>
         </is>
       </c>
       <c r="B948" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -55458,14 +55458,14 @@
     <row r="949" ht="15" customHeight="1">
       <c r="A949" t="inlineStr">
         <is>
-          <t>A 57854-2023</t>
+          <t>A 57916-2023</t>
         </is>
       </c>
       <c r="B949" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -55515,14 +55515,14 @@
     <row r="950" ht="15" customHeight="1">
       <c r="A950" t="inlineStr">
         <is>
-          <t>A 57916-2023</t>
+          <t>A 57917-2023</t>
         </is>
       </c>
       <c r="B950" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         </is>
       </c>
       <c r="G950" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="H950" t="n">
         <v>0</v>
@@ -55572,14 +55572,14 @@
     <row r="951" ht="15" customHeight="1">
       <c r="A951" t="inlineStr">
         <is>
-          <t>A 58283-2023</t>
+          <t>A 58204-2023</t>
         </is>
       </c>
       <c r="B951" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         </is>
       </c>
       <c r="G951" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -55636,7 +55636,7 @@
         <v>45250</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55686,14 +55686,14 @@
     <row r="953" ht="15" customHeight="1">
       <c r="A953" t="inlineStr">
         <is>
-          <t>A 58204-2023</t>
+          <t>A 58283-2023</t>
         </is>
       </c>
       <c r="B953" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         </is>
       </c>
       <c r="G953" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -55750,7 +55750,7 @@
         <v>45250</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>45250</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -55864,7 +55864,7 @@
         <v>45252</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45252</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>45252</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56035,7 +56035,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56092,7 +56092,7 @@
         <v>45257</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56142,14 +56142,14 @@
     <row r="961" ht="15" customHeight="1">
       <c r="A961" t="inlineStr">
         <is>
-          <t>A 59991-2023</t>
+          <t>A 59990-2023</t>
         </is>
       </c>
       <c r="B961" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56162,7 +56162,7 @@
         </is>
       </c>
       <c r="G961" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="H961" t="n">
         <v>0</v>
@@ -56199,14 +56199,14 @@
     <row r="962" ht="15" customHeight="1">
       <c r="A962" t="inlineStr">
         <is>
-          <t>A 59990-2023</t>
+          <t>A 59991-2023</t>
         </is>
       </c>
       <c r="B962" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         </is>
       </c>
       <c r="G962" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -56263,7 +56263,7 @@
         <v>45258</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56313,14 +56313,14 @@
     <row r="964" ht="15" customHeight="1">
       <c r="A964" t="inlineStr">
         <is>
-          <t>A 60277-2023</t>
+          <t>A 60290-2023</t>
         </is>
       </c>
       <c r="B964" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         </is>
       </c>
       <c r="G964" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="H964" t="n">
         <v>0</v>
@@ -56370,14 +56370,14 @@
     <row r="965" ht="15" customHeight="1">
       <c r="A965" t="inlineStr">
         <is>
-          <t>A 60291-2023</t>
+          <t>A 60277-2023</t>
         </is>
       </c>
       <c r="B965" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         </is>
       </c>
       <c r="G965" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -56427,14 +56427,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 60274-2023</t>
+          <t>A 60291-2023</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -56491,7 +56491,7 @@
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56598,14 +56598,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 60290-2023</t>
+          <t>A 60274-2023</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -56655,14 +56655,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 60340-2023</t>
+          <t>A 60441-2023</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56712,14 +56712,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 60441-2023</t>
+          <t>A 60340-2023</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -56769,14 +56769,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 61039-2023</t>
+          <t>A 60986-2023</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -56826,14 +56826,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 60986-2023</t>
+          <t>A 61039-2023</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -56890,7 +56890,7 @@
         <v>45261</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y975"/>
+  <dimension ref="A1:Y979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>45147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>43802</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>44520</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44585</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>43433</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>43860</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>43860</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44120</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>44449</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44455</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44512</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44690</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44872</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>44879</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45140</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45264</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>43334</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>43334</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>43339</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>43339</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>43348</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>43349</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>43349</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>43353</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>43356</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>43358</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>43360</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>43362</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>43363</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>43377</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>43388</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>43390</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43393</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>43393</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>43395</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>43398</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>43412</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>43418</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>43420</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43425</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>43433</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>43433</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>43433</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>43434</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>43436</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>43442</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>43451</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>43454</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>43462</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>43464</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>43464</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>43464</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>43473</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>43474</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>43475</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>43475</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>43479</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>43479</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>43480</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>43482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>43482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>43485</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>43486</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>43489</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>43494</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>43501</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>43504</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>43507</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>43507</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>43507</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>43510</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>43524</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>43530</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>43532</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>43538</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>43546</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>43556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>43556</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>43578</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>43578</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>43592</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>43594</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>43601</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>43601</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>43602</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>43605</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>43606</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>43608</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>43626</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>43653</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>43662</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>43664</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>43670</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43676</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>43684</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43689</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>43689</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>43690</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>43692</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43700</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43700</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43704</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43705</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43705</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>43705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43705</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>43708</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>43710</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>43726</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43727</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43731</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43731</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43731</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43731</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43739</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43739</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43741</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43745</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43748</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43761</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43765</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43770</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43774</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43774</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43784</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43784</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43786</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43787</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43789</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43795</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43795</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43796</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43796</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43798</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43800</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43829</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43842</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43845</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43846</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43854</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43860</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>43860</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43860</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43861</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43861</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>43865</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43865</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43867</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>43868</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>43868</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43868</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43872</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43878</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43879</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43881</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43882</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43886</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43892</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43893</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43893</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43894</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43899</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43899</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43899</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43901</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43901</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43901</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43902</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43903</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43916</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43920</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43923</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43927</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43929</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43966</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43974</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43974</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43979</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43980</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43986</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43992</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>44004</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44004</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>44010</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44040</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44042</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44046</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>44048</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44048</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44054</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44054</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44055</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44060</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44060</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44062</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44068</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44075</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44082</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44084</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44089</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44090</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44105</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44110</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44116</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44120</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>44125</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44130</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44137</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44138</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44147</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44154</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44160</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44161</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44161</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44161</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44161</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44161</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44164</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44165</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44173</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44175</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44179</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44180</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44181</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44182</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44195</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44195</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44195</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44201</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44201</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44204</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44206</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44206</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44215</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44218</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44218</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44220</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44221</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44229</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44236</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44237</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44238</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44245</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44257</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44257</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44265</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44267</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44267</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44267</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>44270</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>44273</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44280</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44294</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44295</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44299</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44299</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44299</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44299</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44306</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44306</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44306</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44309</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44312</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44312</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>44313</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>44313</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44313</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44314</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44319</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44319</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44320</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44325</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>44333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>44333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>44333</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>44334</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44336</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44349</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44351</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>44354</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44354</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>44368</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>44368</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>44371</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44391</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44391</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44393</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44393</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44403</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44404</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>44412</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>44417</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>44418</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>44419</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44421</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>44439</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>44441</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>44442</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>44442</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44443</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44447</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>44447</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44448</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44448</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44453</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44460</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44462</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>44464</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44469</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44470</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>44474</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44474</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44474</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44474</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>44477</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>44477</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44477</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44480</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>44488</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44488</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44488</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44488</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>44488</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>44488</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>44488</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44490</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44491</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>44497</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44497</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>44497</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>44497</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44501</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>44501</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>44503</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>44506</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44509</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44512</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44512</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44512</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44512</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>44512</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44512</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>44512</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44512</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>44514</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>44515</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44515</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44517</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>44518</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>44520</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>44524</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>44524</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>44530</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>44531</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>44532</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44533</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44533</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44533</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44543</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>44543</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44552</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44553</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44558</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>44565</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>44565</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44566</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44567</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>44567</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>44578</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44579</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44587</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44588</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>44593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>44593</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>44594</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>44599</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>44606</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>44606</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>44607</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>44607</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>44607</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>44609</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44609</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44609</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44609</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44613</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>44613</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>44621</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44621</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44624</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44626</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44636</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44636</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44638</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44638</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>44638</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>44638</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44638</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>44641</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>44642</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>44648</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>44649</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>44655</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>44655</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>44655</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>44656</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44656</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44656</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>44657</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44657</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44658</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44658</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>44663</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44663</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>44663</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>44663</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>44663</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>44670</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>44670</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>44672</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>44672</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44674</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>44677</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>44678</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>44678</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44679</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44679</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44685</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44686</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44686</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44692</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44697</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44698</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>44699</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>44705</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>44713</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44715</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44720</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>44724</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44725</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44726</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44733</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44740</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44741</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44749</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44760</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44762</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44763</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44768</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44771</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44771</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44772</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44775</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44776</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44776</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44776</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44781</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44790</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44796</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44800</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44805</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44809</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44809</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44809</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44810</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44810</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44812</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44817</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44823</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44824</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44830</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44831</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44831</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44837</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44837</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44838</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44838</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32531,7 +32531,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>44839</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44841</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44845</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44846</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44847</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44852</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44854</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44858</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44858</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44859</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44861</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44861</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44868</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44869</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44873</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44879</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44880</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44880</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>44881</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>44881</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44881</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>44881</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44882</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>44882</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44882</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>44882</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>44882</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44882</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44883</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44887</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44887</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>44887</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>44888</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>44893</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44893</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44893</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>44894</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>44894</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44895</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44895</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>44896</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>44896</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>44908</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>44908</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>44909</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>44911</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>44914</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>44916</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>44916</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>44917</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44929</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44931</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44944</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44945</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>44945</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44945</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44947</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44947</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44951</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>44951</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>44959</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>44959</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>44959</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>44959</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44959</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>44961</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>44964</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44965</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44966</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44967</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44967</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>44970</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>44971</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44971</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44971</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>44971</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>44971</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>44977</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>44978</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>44992</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>44994</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>44999</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45002</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45002</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45002</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45006</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45006</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45006</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45007</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45008</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45008</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45009</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45015</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45021</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45022</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45022</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45033</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45033</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45035</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>45038</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>45038</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>45038</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>45038</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>45040</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45041</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45042</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45043</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45043</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45043</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45043</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45048</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>45053</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45059</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45062</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>45068</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>45068</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45069</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45069</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45070</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45070</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45070</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45070</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45070</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45070</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45071</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45071</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45071</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45072</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45075</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45078</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45079</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45084</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45084</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45084</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45084</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45084</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>45084</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>45085</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45085</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45087</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45087</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>45087</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45087</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45089</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45091</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45092</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45092</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45093</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45093</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45097</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>45099</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45104</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45104</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45104</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45112</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45114</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45120</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45124</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45132</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45132</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45133</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45134</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45134</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45134</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45134</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45134</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45134</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45134</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45134</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45139</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45140</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45140</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45140</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45140</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45140</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45140</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45141</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45147</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45147</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>45152</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45153</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45153</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45154</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45154</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45155</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45157</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45157</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45157</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45158</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45159</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45159</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45160</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45160</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45161</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45161</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45161</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45161</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45162</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45162</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>45162</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45162</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45162</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45788,7 +45788,7 @@
         <v>45162</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>45162</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>45162</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45162</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45162</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>45162</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45162</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46187,7 +46187,7 @@
         <v>45162</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>45163</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45163</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45163</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>45163</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45163</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45163</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>45163</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45166</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46700,7 +46700,7 @@
         <v>45166</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>45166</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45166</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45166</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45166</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45166</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45167</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45167</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45167</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45167</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45168</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45168</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45168</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>45169</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>45170</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45173</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45173</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45173</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45173</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>45173</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45174</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47897,7 +47897,7 @@
         <v>45176</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47954,7 +47954,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48068,7 +48068,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>45176</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45180</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>45182</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45187</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45189</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45189</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45190</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45190</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>45190</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49151,7 +49151,7 @@
         <v>45191</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49208,7 +49208,7 @@
         <v>45194</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45194</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45194</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45194</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45199</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45199</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45203</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49897,7 +49897,7 @@
         <v>45209</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45211</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>45211</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>45212</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50125,7 +50125,7 @@
         <v>45215</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45217</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50296,7 +50296,7 @@
         <v>45217</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>45217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50638,7 +50638,7 @@
         <v>45222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>45223</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50866,7 +50866,7 @@
         <v>45224</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>45224</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>45224</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45224</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>45225</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45225</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45225</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51265,7 +51265,7 @@
         <v>45225</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45225</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>45225</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45225</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51493,7 +51493,7 @@
         <v>45225</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45225</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45226</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45227</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>45227</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51778,7 +51778,7 @@
         <v>45227</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45227</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>45227</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51949,7 +51949,7 @@
         <v>45227</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52006,7 +52006,7 @@
         <v>45230</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>45230</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52120,7 +52120,7 @@
         <v>45231</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52182,7 +52182,7 @@
         <v>45231</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45231</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>45231</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45231</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45233</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52472,7 +52472,7 @@
         <v>45233</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52529,7 +52529,7 @@
         <v>45233</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         <v>45233</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>45233</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45233</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45233</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>45233</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>45233</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45236</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
         <v>45236</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>45236</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>45236</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53149,14 +53149,14 @@
     <row r="908" ht="15" customHeight="1">
       <c r="A908" t="inlineStr">
         <is>
-          <t>A 54904-2023</t>
+          <t>A 54906-2023</t>
         </is>
       </c>
       <c r="B908" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         </is>
       </c>
       <c r="G908" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -53206,14 +53206,14 @@
     <row r="909" ht="15" customHeight="1">
       <c r="A909" t="inlineStr">
         <is>
-          <t>A 54914-2023</t>
+          <t>A 54912-2023</t>
         </is>
       </c>
       <c r="B909" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53226,7 +53226,7 @@
         </is>
       </c>
       <c r="G909" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="H909" t="n">
         <v>0</v>
@@ -53263,14 +53263,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 54906-2023</t>
+          <t>A 54904-2023</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53283,7 +53283,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53320,14 +53320,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 54912-2023</t>
+          <t>A 54914-2023</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53340,7 +53340,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53384,7 +53384,7 @@
         <v>45236</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53441,7 +53441,7 @@
         <v>45236</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53491,14 +53491,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 55309-2023</t>
+          <t>A 55160-2023</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53511,7 +53511,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -53548,14 +53548,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 55160-2023</t>
+          <t>A 55267-2023</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53612,7 +53612,7 @@
         <v>45237</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53669,7 +53669,7 @@
         <v>45237</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53719,14 +53719,14 @@
     <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>A 55267-2023</t>
+          <t>A 55309-2023</t>
         </is>
       </c>
       <c r="B918" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -53783,7 +53783,7 @@
         <v>45239</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53840,7 +53840,7 @@
         <v>45239</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53897,7 +53897,7 @@
         <v>45242</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>45242</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>45243</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54061,14 +54061,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 56778-2023</t>
+          <t>A 56775-2023</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54118,14 +54118,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 56786-2023</t>
+          <t>A 56780-2023</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54138,7 +54138,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54175,14 +54175,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 56794-2023</t>
+          <t>A 56784-2023</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54195,7 +54195,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54232,14 +54232,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 56802-2023</t>
+          <t>A 56796-2023</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54289,14 +54289,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 56779-2023</t>
+          <t>A 56804-2023</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54346,14 +54346,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 56791-2023</t>
+          <t>A 56779-2023</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54403,14 +54403,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 56795-2023</t>
+          <t>A 56791-2023</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54460,14 +54460,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 56799-2023</t>
+          <t>A 56795-2023</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54517,14 +54517,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 56775-2023</t>
+          <t>A 56799-2023</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54574,14 +54574,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 56780-2023</t>
+          <t>A 56778-2023</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54631,14 +54631,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 56784-2023</t>
+          <t>A 56786-2023</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54688,14 +54688,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 56796-2023</t>
+          <t>A 56794-2023</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54745,14 +54745,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 56804-2023</t>
+          <t>A 56802-2023</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54809,7 +54809,7 @@
         <v>45244</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45244</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45244</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45244</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55030,14 +55030,14 @@
     <row r="941" ht="15" customHeight="1">
       <c r="A941" t="inlineStr">
         <is>
-          <t>A 57173-2023</t>
+          <t>A 57215-2023</t>
         </is>
       </c>
       <c r="B941" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="H941" t="n">
         <v>0</v>
@@ -55087,14 +55087,14 @@
     <row r="942" ht="15" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>A 57215-2023</t>
+          <t>A 57173-2023</t>
         </is>
       </c>
       <c r="B942" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -55151,7 +55151,7 @@
         <v>45245</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45245</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45245</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>45246</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55379,7 +55379,7 @@
         <v>45246</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45246</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55493,7 +55493,7 @@
         <v>45247</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>45247</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>45247</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55657,14 +55657,14 @@
     <row r="952" ht="15" customHeight="1">
       <c r="A952" t="inlineStr">
         <is>
-          <t>A 58204-2023</t>
+          <t>A 58283-2023</t>
         </is>
       </c>
       <c r="B952" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55677,7 +55677,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -55714,14 +55714,14 @@
     <row r="953" ht="15" customHeight="1">
       <c r="A953" t="inlineStr">
         <is>
-          <t>A 58283-2023</t>
+          <t>A 58204-2023</t>
         </is>
       </c>
       <c r="B953" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         </is>
       </c>
       <c r="G953" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -55771,14 +55771,14 @@
     <row r="954" ht="15" customHeight="1">
       <c r="A954" t="inlineStr">
         <is>
-          <t>A 58403-2023</t>
+          <t>A 58401-2023</t>
         </is>
       </c>
       <c r="B954" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         </is>
       </c>
       <c r="G954" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="H954" t="n">
         <v>0</v>
@@ -55828,14 +55828,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 58401-2023</t>
+          <t>A 58426-2023</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -55885,14 +55885,14 @@
     <row r="956" ht="15" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>A 58426-2023</t>
+          <t>A 58403-2023</t>
         </is>
       </c>
       <c r="B956" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -55942,14 +55942,14 @@
     <row r="957" ht="15" customHeight="1">
       <c r="A957" t="inlineStr">
         <is>
-          <t>A 59075-2023</t>
+          <t>A 58917-2023</t>
         </is>
       </c>
       <c r="B957" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="H957" t="n">
         <v>0</v>
@@ -55999,14 +55999,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 58917-2023</t>
+          <t>A 59075-2023</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56063,7 +56063,7 @@
         <v>45252</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>45257</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45257</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45257</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45258</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45258</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56455,14 +56455,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 60277-2023</t>
+          <t>A 60293-2023</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -56512,14 +56512,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 60291-2023</t>
+          <t>A 60277-2023</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56569,14 +56569,14 @@
     <row r="968" ht="15" customHeight="1">
       <c r="A968" t="inlineStr">
         <is>
-          <t>A 60293-2023</t>
+          <t>A 60291-2023</t>
         </is>
       </c>
       <c r="B968" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         </is>
       </c>
       <c r="G968" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -56633,7 +56633,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56690,7 +56690,7 @@
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56740,14 +56740,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 60441-2023</t>
+          <t>A 60340-2023</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56760,7 +56760,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -56797,14 +56797,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 60340-2023</t>
+          <t>A 60441-2023</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -56817,7 +56817,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -56854,14 +56854,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 60912-2023</t>
+          <t>A 60986-2023</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -56911,14 +56911,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 60986-2023</t>
+          <t>A 61039-2023</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -56931,7 +56931,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -56965,62 +56965,290 @@
       </c>
       <c r="R974" s="2" t="inlineStr"/>
     </row>
-    <row r="975">
+    <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 61039-2023</t>
+          <t>A 60912-2023</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C975" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G975" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H975" t="n">
+        <v>0</v>
+      </c>
+      <c r="I975" t="n">
+        <v>0</v>
+      </c>
+      <c r="J975" t="n">
+        <v>0</v>
+      </c>
+      <c r="K975" t="n">
+        <v>0</v>
+      </c>
+      <c r="L975" t="n">
+        <v>0</v>
+      </c>
+      <c r="M975" t="n">
+        <v>0</v>
+      </c>
+      <c r="N975" t="n">
+        <v>0</v>
+      </c>
+      <c r="O975" t="n">
+        <v>0</v>
+      </c>
+      <c r="P975" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q975" t="n">
+        <v>0</v>
+      </c>
+      <c r="R975" s="2" t="inlineStr"/>
+    </row>
+    <row r="976" ht="15" customHeight="1">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>A 61510-2023</t>
+        </is>
+      </c>
+      <c r="B976" s="1" t="n">
         <v>45265</v>
       </c>
-      <c r="D975" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E975" t="inlineStr">
-        <is>
-          <t>ULRICEHAMN</t>
-        </is>
-      </c>
-      <c r="G975" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H975" t="n">
-        <v>0</v>
-      </c>
-      <c r="I975" t="n">
-        <v>0</v>
-      </c>
-      <c r="J975" t="n">
-        <v>0</v>
-      </c>
-      <c r="K975" t="n">
-        <v>0</v>
-      </c>
-      <c r="L975" t="n">
-        <v>0</v>
-      </c>
-      <c r="M975" t="n">
-        <v>0</v>
-      </c>
-      <c r="N975" t="n">
-        <v>0</v>
-      </c>
-      <c r="O975" t="n">
-        <v>0</v>
-      </c>
-      <c r="P975" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q975" t="n">
-        <v>0</v>
-      </c>
-      <c r="R975" s="2" t="inlineStr"/>
+      <c r="C976" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G976" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H976" t="n">
+        <v>0</v>
+      </c>
+      <c r="I976" t="n">
+        <v>0</v>
+      </c>
+      <c r="J976" t="n">
+        <v>0</v>
+      </c>
+      <c r="K976" t="n">
+        <v>0</v>
+      </c>
+      <c r="L976" t="n">
+        <v>0</v>
+      </c>
+      <c r="M976" t="n">
+        <v>0</v>
+      </c>
+      <c r="N976" t="n">
+        <v>0</v>
+      </c>
+      <c r="O976" t="n">
+        <v>0</v>
+      </c>
+      <c r="P976" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q976" t="n">
+        <v>0</v>
+      </c>
+      <c r="R976" s="2" t="inlineStr"/>
+    </row>
+    <row r="977" ht="15" customHeight="1">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>A 61508-2023</t>
+        </is>
+      </c>
+      <c r="B977" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C977" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G977" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H977" t="n">
+        <v>0</v>
+      </c>
+      <c r="I977" t="n">
+        <v>0</v>
+      </c>
+      <c r="J977" t="n">
+        <v>0</v>
+      </c>
+      <c r="K977" t="n">
+        <v>0</v>
+      </c>
+      <c r="L977" t="n">
+        <v>0</v>
+      </c>
+      <c r="M977" t="n">
+        <v>0</v>
+      </c>
+      <c r="N977" t="n">
+        <v>0</v>
+      </c>
+      <c r="O977" t="n">
+        <v>0</v>
+      </c>
+      <c r="P977" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q977" t="n">
+        <v>0</v>
+      </c>
+      <c r="R977" s="2" t="inlineStr"/>
+    </row>
+    <row r="978" ht="15" customHeight="1">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>A 61512-2023</t>
+        </is>
+      </c>
+      <c r="B978" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C978" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G978" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H978" t="n">
+        <v>0</v>
+      </c>
+      <c r="I978" t="n">
+        <v>0</v>
+      </c>
+      <c r="J978" t="n">
+        <v>0</v>
+      </c>
+      <c r="K978" t="n">
+        <v>0</v>
+      </c>
+      <c r="L978" t="n">
+        <v>0</v>
+      </c>
+      <c r="M978" t="n">
+        <v>0</v>
+      </c>
+      <c r="N978" t="n">
+        <v>0</v>
+      </c>
+      <c r="O978" t="n">
+        <v>0</v>
+      </c>
+      <c r="P978" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q978" t="n">
+        <v>0</v>
+      </c>
+      <c r="R978" s="2" t="inlineStr"/>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>A 61647-2023</t>
+        </is>
+      </c>
+      <c r="B979" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C979" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G979" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H979" t="n">
+        <v>0</v>
+      </c>
+      <c r="I979" t="n">
+        <v>0</v>
+      </c>
+      <c r="J979" t="n">
+        <v>0</v>
+      </c>
+      <c r="K979" t="n">
+        <v>0</v>
+      </c>
+      <c r="L979" t="n">
+        <v>0</v>
+      </c>
+      <c r="M979" t="n">
+        <v>0</v>
+      </c>
+      <c r="N979" t="n">
+        <v>0</v>
+      </c>
+      <c r="O979" t="n">
+        <v>0</v>
+      </c>
+      <c r="P979" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q979" t="n">
+        <v>0</v>
+      </c>
+      <c r="R979" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y979"/>
+  <dimension ref="A1:Y981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>45147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>43802</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>44520</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44585</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>43433</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>43860</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>43860</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44120</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>44449</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44455</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44512</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44690</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44872</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>44879</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45140</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45264</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>43334</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>43334</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>43339</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>43339</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>43348</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>43349</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>43349</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>43353</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>43356</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>43358</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>43360</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>43362</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>43363</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>43377</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>43388</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>43390</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43393</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>43393</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>43395</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>43398</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>43412</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>43418</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>43420</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43425</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>43433</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>43433</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>43433</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>43434</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>43436</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>43442</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>43451</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>43454</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>43462</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>43464</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>43464</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>43464</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>43473</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>43474</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>43475</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>43475</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>43479</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>43479</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>43480</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>43482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>43482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>43485</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>43486</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>43489</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>43494</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>43501</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>43504</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>43507</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>43507</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>43507</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>43510</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>43524</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>43530</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>43532</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>43538</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>43546</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>43556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>43556</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>43578</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>43578</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>43592</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>43594</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>43601</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>43601</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>43602</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>43605</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>43606</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>43608</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>43626</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>43653</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>43662</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>43664</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>43670</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43676</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>43684</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43689</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>43689</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>43690</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>43692</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43700</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43700</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43704</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43705</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43705</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>43705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43705</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>43708</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>43710</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>43726</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43727</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43731</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43731</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43731</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43731</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43739</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43739</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43741</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43745</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43748</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43761</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43765</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43770</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43774</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43774</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43784</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43784</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43786</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43787</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43789</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43795</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43795</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43796</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43796</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43798</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43800</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43829</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43842</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43845</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43846</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43854</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43860</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>43860</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43860</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43861</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43861</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>43865</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43865</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43867</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>43868</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>43868</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43868</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43872</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43878</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43879</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43881</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43882</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43886</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43892</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43893</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43893</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43894</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43899</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43899</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43899</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43901</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43901</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43901</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43902</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43903</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43916</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43920</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43923</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43927</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43929</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43966</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43974</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43974</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43979</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43980</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43986</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43992</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>44004</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44004</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>44010</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44040</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44042</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44046</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>44048</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44048</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44054</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44054</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44055</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44060</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44060</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44062</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44068</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44075</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44082</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44084</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44089</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44090</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44105</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44110</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44116</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44120</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>44125</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44130</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44137</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44138</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44147</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44154</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44160</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44161</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44161</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44161</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44161</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44161</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44164</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44165</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44173</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44175</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44179</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44180</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44181</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44182</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44195</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44195</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44195</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44201</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44201</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44204</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44206</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44206</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44215</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44218</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44218</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44220</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44221</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44229</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44236</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44237</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44238</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44245</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44257</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44257</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44265</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44267</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44267</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44267</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>44270</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>44273</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44280</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44294</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44295</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44299</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44299</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44299</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44299</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44306</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44306</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44306</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44309</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44312</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44312</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>44313</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>44313</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44313</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44314</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44319</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44319</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44320</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44325</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>44333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>44333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>44333</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>44334</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44336</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44349</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44351</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>44354</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44354</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>44368</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>44368</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>44371</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44391</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44391</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44393</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44393</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44403</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44404</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>44412</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>44417</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>44418</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>44419</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44421</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>44439</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>44441</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>44442</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>44442</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44443</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44447</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>44447</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44448</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44448</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44453</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44460</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44462</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>44464</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44469</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44470</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>44474</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44474</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44474</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44474</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>44477</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>44477</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44477</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44480</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>44488</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44488</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44488</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44488</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>44488</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>44488</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>44488</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44490</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44491</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>44497</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44497</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>44497</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>44497</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44501</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>44501</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>44503</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>44506</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44509</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44512</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44512</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44512</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44512</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>44512</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44512</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>44512</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44512</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>44514</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>44515</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44515</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44517</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>44518</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>44520</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>44524</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>44524</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>44530</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>44531</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>44532</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44533</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44533</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44533</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44543</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>44543</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44552</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44553</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44558</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>44565</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>44565</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44566</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44567</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>44567</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>44578</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44579</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44587</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44588</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>44593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>44593</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>44594</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>44599</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>44606</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>44606</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>44607</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>44607</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>44607</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>44609</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44609</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44609</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44609</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44613</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>44613</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>44621</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44621</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44624</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44626</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44636</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44636</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44638</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44638</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>44638</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>44638</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44638</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>44641</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>44642</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>44648</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>44649</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>44655</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>44655</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>44655</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>44656</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44656</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44656</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>44657</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44657</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44658</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44658</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>44663</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44663</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>44663</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>44663</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>44663</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>44670</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>44670</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>44672</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>44672</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44674</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>44677</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>44678</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>44678</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44679</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44679</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44685</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44686</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44686</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44692</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44697</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44698</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>44699</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>44705</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>44713</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44715</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44720</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>44724</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44725</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44726</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44733</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44740</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44741</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44749</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44760</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44762</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44763</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44768</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44771</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44771</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44772</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44775</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44776</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44776</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44776</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44781</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44790</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44796</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44800</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44805</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44809</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44809</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44809</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44810</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44810</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44812</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44817</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44823</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44824</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44830</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44831</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44831</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44837</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44837</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44838</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44838</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32531,7 +32531,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>44839</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44841</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44845</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44846</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44847</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44852</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44854</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44858</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44858</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44859</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44861</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44861</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44868</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44869</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44873</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44879</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44880</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44880</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>44881</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>44881</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44881</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>44881</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44882</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>44882</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44882</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>44882</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>44882</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44882</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44883</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44887</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44887</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>44887</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>44888</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>44893</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44893</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44893</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>44894</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>44894</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44895</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44895</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>44896</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>44896</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>44908</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>44908</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>44909</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>44911</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>44914</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>44916</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>44916</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>44917</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44929</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44931</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44944</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44945</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>44945</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44945</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44947</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44947</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44951</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>44951</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>44959</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>44959</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>44959</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>44959</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44959</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>44961</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>44964</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44965</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44966</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44967</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44967</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>44970</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>44971</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44971</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44971</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>44971</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>44971</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>44977</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>44978</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>44992</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>44994</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>44999</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45002</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45002</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45002</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45006</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45006</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45006</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45007</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45008</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45008</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45009</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45015</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45021</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45022</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45022</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45033</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45033</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45035</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>45038</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>45038</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>45038</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>45038</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>45040</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45041</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45042</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45043</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45043</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45043</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45043</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45048</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>45053</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45059</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45062</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>45068</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>45068</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45069</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45069</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45070</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45070</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45070</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45070</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45070</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45070</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45071</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45071</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45071</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45072</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45075</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45078</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45079</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45084</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45084</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45084</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45084</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45084</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>45084</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>45085</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45085</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45087</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45087</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>45087</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45087</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45089</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45091</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45092</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45092</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45093</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45093</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45097</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>45099</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45104</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45104</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45104</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45112</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45114</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45120</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45124</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45132</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45132</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45133</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45134</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45134</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45134</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45134</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45134</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45134</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45134</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45134</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45139</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45140</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45140</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45140</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45140</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45140</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45140</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45141</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45147</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45147</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>45152</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45153</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45153</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45154</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45154</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45155</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45157</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45157</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45157</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45158</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45159</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45159</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45160</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45160</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45161</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45161</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45161</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45161</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45162</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45162</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>45162</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45162</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45162</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45788,7 +45788,7 @@
         <v>45162</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>45162</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>45162</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45162</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45162</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>45162</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45162</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46187,7 +46187,7 @@
         <v>45162</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>45163</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45163</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45163</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>45163</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45163</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45163</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>45163</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45166</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46700,7 +46700,7 @@
         <v>45166</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>45166</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45166</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45166</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45166</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45166</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45167</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45167</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45167</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45167</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45168</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45168</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45168</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>45169</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>45170</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45173</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45173</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45173</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45173</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>45173</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45174</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47897,7 +47897,7 @@
         <v>45176</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47954,7 +47954,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48068,7 +48068,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>45176</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45180</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>45182</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45187</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45189</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45189</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45190</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45190</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>45190</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49151,7 +49151,7 @@
         <v>45191</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49208,7 +49208,7 @@
         <v>45194</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45194</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45194</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45194</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45199</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45199</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45203</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49897,7 +49897,7 @@
         <v>45209</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45211</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>45211</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>45212</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50125,7 +50125,7 @@
         <v>45215</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45217</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50296,7 +50296,7 @@
         <v>45217</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>45217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50638,7 +50638,7 @@
         <v>45222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>45223</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50866,7 +50866,7 @@
         <v>45224</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>45224</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>45224</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45224</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>45225</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45225</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45225</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51265,7 +51265,7 @@
         <v>45225</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45225</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>45225</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45225</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51493,7 +51493,7 @@
         <v>45225</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45225</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45226</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45227</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>45227</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51778,7 +51778,7 @@
         <v>45227</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45227</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>45227</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51949,7 +51949,7 @@
         <v>45227</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52006,7 +52006,7 @@
         <v>45230</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>45230</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52120,7 +52120,7 @@
         <v>45231</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52182,7 +52182,7 @@
         <v>45231</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45231</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>45231</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45231</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45233</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52472,7 +52472,7 @@
         <v>45233</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52529,7 +52529,7 @@
         <v>45233</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         <v>45233</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>45233</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45233</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45233</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>45233</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>45233</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45236</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
         <v>45236</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>45236</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>45236</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53156,7 +53156,7 @@
         <v>45236</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>45236</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53270,7 +53270,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53327,7 +53327,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53384,7 +53384,7 @@
         <v>45236</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53441,7 +53441,7 @@
         <v>45236</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53498,7 +53498,7 @@
         <v>45237</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>45237</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45237</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53669,7 +53669,7 @@
         <v>45237</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>45237</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53776,14 +53776,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 55763-2023</t>
+          <t>A 55765-2023</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53833,14 +53833,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 55765-2023</t>
+          <t>A 55763-2023</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53897,7 +53897,7 @@
         <v>45242</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>45242</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>45243</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54182,7 +54182,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54296,7 +54296,7 @@
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54346,14 +54346,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 56779-2023</t>
+          <t>A 56717-2023</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54403,14 +54403,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 56791-2023</t>
+          <t>A 56772-2023</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54460,14 +54460,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 56795-2023</t>
+          <t>A 56776-2023</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54517,14 +54517,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 56799-2023</t>
+          <t>A 56793-2023</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54574,14 +54574,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 56778-2023</t>
+          <t>A 56779-2023</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54631,14 +54631,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 56786-2023</t>
+          <t>A 56791-2023</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54688,14 +54688,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 56794-2023</t>
+          <t>A 56795-2023</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54745,14 +54745,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 56802-2023</t>
+          <t>A 56799-2023</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54802,14 +54802,14 @@
     <row r="937" ht="15" customHeight="1">
       <c r="A937" t="inlineStr">
         <is>
-          <t>A 56717-2023</t>
+          <t>A 56778-2023</t>
         </is>
       </c>
       <c r="B937" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         </is>
       </c>
       <c r="G937" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H937" t="n">
         <v>0</v>
@@ -54859,14 +54859,14 @@
     <row r="938" ht="15" customHeight="1">
       <c r="A938" t="inlineStr">
         <is>
-          <t>A 56772-2023</t>
+          <t>A 56786-2023</t>
         </is>
       </c>
       <c r="B938" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         </is>
       </c>
       <c r="G938" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H938" t="n">
         <v>0</v>
@@ -54916,14 +54916,14 @@
     <row r="939" ht="15" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>A 56776-2023</t>
+          <t>A 56794-2023</t>
         </is>
       </c>
       <c r="B939" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -54973,14 +54973,14 @@
     <row r="940" ht="15" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>A 56793-2023</t>
+          <t>A 56802-2023</t>
         </is>
       </c>
       <c r="B940" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -55030,14 +55030,14 @@
     <row r="941" ht="15" customHeight="1">
       <c r="A941" t="inlineStr">
         <is>
-          <t>A 57215-2023</t>
+          <t>A 57170-2023</t>
         </is>
       </c>
       <c r="B941" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="H941" t="n">
         <v>0</v>
@@ -55094,7 +55094,7 @@
         <v>45245</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55144,14 +55144,14 @@
     <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
-          <t>A 57170-2023</t>
+          <t>A 57196-2023</t>
         </is>
       </c>
       <c r="B943" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55201,14 +55201,14 @@
     <row r="944" ht="15" customHeight="1">
       <c r="A944" t="inlineStr">
         <is>
-          <t>A 57204-2023</t>
+          <t>A 57215-2023</t>
         </is>
       </c>
       <c r="B944" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -55258,14 +55258,14 @@
     <row r="945" ht="15" customHeight="1">
       <c r="A945" t="inlineStr">
         <is>
-          <t>A 57196-2023</t>
+          <t>A 57204-2023</t>
         </is>
       </c>
       <c r="B945" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         </is>
       </c>
       <c r="G945" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -55322,7 +55322,7 @@
         <v>45246</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55379,7 +55379,7 @@
         <v>45246</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45246</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55493,7 +55493,7 @@
         <v>45247</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>45247</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>45247</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45250</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55714,14 +55714,14 @@
     <row r="953" ht="15" customHeight="1">
       <c r="A953" t="inlineStr">
         <is>
-          <t>A 58204-2023</t>
+          <t>A 58401-2023</t>
         </is>
       </c>
       <c r="B953" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         </is>
       </c>
       <c r="G953" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -55771,14 +55771,14 @@
     <row r="954" ht="15" customHeight="1">
       <c r="A954" t="inlineStr">
         <is>
-          <t>A 58401-2023</t>
+          <t>A 58426-2023</t>
         </is>
       </c>
       <c r="B954" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         </is>
       </c>
       <c r="G954" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="H954" t="n">
         <v>0</v>
@@ -55828,14 +55828,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 58426-2023</t>
+          <t>A 58403-2023</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -55885,14 +55885,14 @@
     <row r="956" ht="15" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>A 58403-2023</t>
+          <t>A 58204-2023</t>
         </is>
       </c>
       <c r="B956" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -55949,7 +55949,7 @@
         <v>45252</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -55999,14 +55999,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 59075-2023</t>
+          <t>A 59036-2023</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56056,14 +56056,14 @@
     <row r="959" ht="15" customHeight="1">
       <c r="A959" t="inlineStr">
         <is>
-          <t>A 59036-2023</t>
+          <t>A 59075-2023</t>
         </is>
       </c>
       <c r="B959" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         </is>
       </c>
       <c r="G959" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H959" t="n">
         <v>0</v>
@@ -56120,7 +56120,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>45257</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45257</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45257</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56341,14 +56341,14 @@
     <row r="964" ht="15" customHeight="1">
       <c r="A964" t="inlineStr">
         <is>
-          <t>A 60084-2023</t>
+          <t>A 60016-2023</t>
         </is>
       </c>
       <c r="B964" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         </is>
       </c>
       <c r="G964" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="H964" t="n">
         <v>0</v>
@@ -56398,14 +56398,14 @@
     <row r="965" ht="15" customHeight="1">
       <c r="A965" t="inlineStr">
         <is>
-          <t>A 60016-2023</t>
+          <t>A 60277-2023</t>
         </is>
       </c>
       <c r="B965" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56418,7 +56418,7 @@
         </is>
       </c>
       <c r="G965" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -56455,14 +56455,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 60293-2023</t>
+          <t>A 60291-2023</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -56512,14 +56512,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 60277-2023</t>
+          <t>A 60084-2023</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56569,14 +56569,14 @@
     <row r="968" ht="15" customHeight="1">
       <c r="A968" t="inlineStr">
         <is>
-          <t>A 60291-2023</t>
+          <t>A 60274-2023</t>
         </is>
       </c>
       <c r="B968" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         </is>
       </c>
       <c r="G968" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -56626,14 +56626,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 60290-2023</t>
+          <t>A 60293-2023</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -56683,14 +56683,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 60274-2023</t>
+          <t>A 60290-2023</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56747,7 +56747,7 @@
         <v>45259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45259</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -56854,14 +56854,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 60986-2023</t>
+          <t>A 60912-2023</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -56911,14 +56911,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 61039-2023</t>
+          <t>A 60986-2023</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -56931,7 +56931,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -56968,14 +56968,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 60912-2023</t>
+          <t>A 61039-2023</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -56988,7 +56988,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -57025,14 +57025,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 61510-2023</t>
+          <t>A 61508-2023</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57045,7 +57045,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -57082,14 +57082,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 61508-2023</t>
+          <t>A 61512-2023</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57102,7 +57102,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -57139,14 +57139,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 61512-2023</t>
+          <t>A 61647-2023</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57193,62 +57193,176 @@
       </c>
       <c r="R978" s="2" t="inlineStr"/>
     </row>
-    <row r="979">
+    <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 61647-2023</t>
+          <t>A 61510-2023</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C979" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G979" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H979" t="n">
+        <v>0</v>
+      </c>
+      <c r="I979" t="n">
+        <v>0</v>
+      </c>
+      <c r="J979" t="n">
+        <v>0</v>
+      </c>
+      <c r="K979" t="n">
+        <v>0</v>
+      </c>
+      <c r="L979" t="n">
+        <v>0</v>
+      </c>
+      <c r="M979" t="n">
+        <v>0</v>
+      </c>
+      <c r="N979" t="n">
+        <v>0</v>
+      </c>
+      <c r="O979" t="n">
+        <v>0</v>
+      </c>
+      <c r="P979" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q979" t="n">
+        <v>0</v>
+      </c>
+      <c r="R979" s="2" t="inlineStr"/>
+    </row>
+    <row r="980" ht="15" customHeight="1">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>A 61827-2023</t>
+        </is>
+      </c>
+      <c r="B980" s="1" t="n">
         <v>45266</v>
       </c>
-      <c r="D979" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E979" t="inlineStr">
-        <is>
-          <t>ULRICEHAMN</t>
-        </is>
-      </c>
-      <c r="G979" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H979" t="n">
-        <v>0</v>
-      </c>
-      <c r="I979" t="n">
-        <v>0</v>
-      </c>
-      <c r="J979" t="n">
-        <v>0</v>
-      </c>
-      <c r="K979" t="n">
-        <v>0</v>
-      </c>
-      <c r="L979" t="n">
-        <v>0</v>
-      </c>
-      <c r="M979" t="n">
-        <v>0</v>
-      </c>
-      <c r="N979" t="n">
-        <v>0</v>
-      </c>
-      <c r="O979" t="n">
-        <v>0</v>
-      </c>
-      <c r="P979" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q979" t="n">
-        <v>0</v>
-      </c>
-      <c r="R979" s="2" t="inlineStr"/>
+      <c r="C980" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G980" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H980" t="n">
+        <v>0</v>
+      </c>
+      <c r="I980" t="n">
+        <v>0</v>
+      </c>
+      <c r="J980" t="n">
+        <v>0</v>
+      </c>
+      <c r="K980" t="n">
+        <v>0</v>
+      </c>
+      <c r="L980" t="n">
+        <v>0</v>
+      </c>
+      <c r="M980" t="n">
+        <v>0</v>
+      </c>
+      <c r="N980" t="n">
+        <v>0</v>
+      </c>
+      <c r="O980" t="n">
+        <v>0</v>
+      </c>
+      <c r="P980" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q980" t="n">
+        <v>0</v>
+      </c>
+      <c r="R980" s="2" t="inlineStr"/>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>A 61943-2023</t>
+        </is>
+      </c>
+      <c r="B981" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C981" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>ULRICEHAMN</t>
+        </is>
+      </c>
+      <c r="G981" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H981" t="n">
+        <v>0</v>
+      </c>
+      <c r="I981" t="n">
+        <v>0</v>
+      </c>
+      <c r="J981" t="n">
+        <v>0</v>
+      </c>
+      <c r="K981" t="n">
+        <v>0</v>
+      </c>
+      <c r="L981" t="n">
+        <v>0</v>
+      </c>
+      <c r="M981" t="n">
+        <v>0</v>
+      </c>
+      <c r="N981" t="n">
+        <v>0</v>
+      </c>
+      <c r="O981" t="n">
+        <v>0</v>
+      </c>
+      <c r="P981" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q981" t="n">
+        <v>0</v>
+      </c>
+      <c r="R981" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -564,7 +564,7 @@
         <v>45147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>43802</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>44520</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44585</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>43433</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>43860</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>43860</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44120</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>44449</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44455</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44512</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44690</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44872</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>44879</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45140</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45264</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>43334</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>43334</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>43339</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>43339</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>43348</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>43349</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>43349</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>43353</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>43356</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>43358</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>43360</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>43362</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>43363</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>43377</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>43388</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>43390</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43393</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>43393</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>43395</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>43398</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>43412</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>43418</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>43420</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43425</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>43433</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>43433</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>43433</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>43434</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>43436</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>43442</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>43451</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>43454</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>43462</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>43464</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>43464</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>43464</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>43473</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>43474</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>43475</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>43475</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>43479</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>43479</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>43480</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>43482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>43482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>43485</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>43486</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>43489</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>43494</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>43501</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>43504</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>43507</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>43507</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>43507</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>43510</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>43524</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>43530</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>43532</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>43538</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>43546</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>43556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>43556</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>43578</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>43578</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>43592</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>43594</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>43601</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>43601</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>43602</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>43605</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>43606</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>43608</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>43626</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>43653</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>43662</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>43664</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>43670</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43676</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>43684</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43689</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>43689</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>43690</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>43692</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43700</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43700</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43704</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43705</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43705</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>43705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43705</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>43708</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>43710</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>43726</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43727</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43731</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43731</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43731</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43731</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43739</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43739</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43741</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43745</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43748</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43761</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43765</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43770</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43774</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43774</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43784</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43784</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43786</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43787</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43789</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43795</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43795</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43796</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43796</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43798</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43800</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43829</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43842</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43845</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43846</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43854</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43860</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>43860</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43860</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43861</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43861</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>43865</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43865</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43867</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>43868</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>43868</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43868</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43872</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43878</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43879</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43881</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43882</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43886</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43892</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43893</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43893</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43894</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43899</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43899</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43899</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43901</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43901</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43901</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43902</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43903</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43916</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43920</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43923</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43927</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43929</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43966</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43974</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43974</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43979</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43980</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43986</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43992</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>44004</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44004</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>44010</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44040</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44042</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44046</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>44048</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44048</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44054</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44054</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44055</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44060</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44060</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44062</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44068</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44075</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44082</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44084</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44089</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44090</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44105</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44110</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44116</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44120</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>44125</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44130</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44137</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44138</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44147</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44154</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44160</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44161</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44161</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44161</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44161</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44161</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44164</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44165</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44173</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44175</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44179</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44180</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44181</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44182</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44195</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44195</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44195</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44201</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44201</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44204</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44206</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44206</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44215</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44218</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44218</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44220</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44221</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44229</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44236</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44237</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44238</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44245</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44257</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44257</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44265</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44267</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44267</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44267</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>44270</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>44273</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44280</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44294</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44295</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44299</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44299</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44299</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44299</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44306</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44306</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44306</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44309</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44312</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44312</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>44313</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>44313</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44313</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44314</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44319</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44319</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44320</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44325</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>44333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>44333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>44333</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>44334</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44336</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44349</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44351</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>44354</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44354</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>44368</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>44368</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>44371</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44391</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44391</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44393</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44393</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44403</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44404</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>44412</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>44417</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>44418</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>44419</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44421</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>44439</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>44441</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>44442</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>44442</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44443</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44447</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>44447</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44448</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44448</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44453</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44460</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44462</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>44464</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44469</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44470</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>44474</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44474</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44474</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44474</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>44477</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>44477</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44477</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44480</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>44488</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44488</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44488</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44488</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>44488</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>44488</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>44488</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44490</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44491</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>44497</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44497</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>44497</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>44497</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44501</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>44501</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>44503</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>44506</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44509</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44512</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44512</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44512</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44512</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>44512</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44512</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>44512</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44512</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>44514</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>44515</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44515</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44517</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>44518</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>44520</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>44524</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>44524</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>44530</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>44531</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>44532</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44533</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44533</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44533</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44543</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>44543</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44552</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44553</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44558</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>44565</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>44565</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44566</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44567</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>44567</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>44578</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44579</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44587</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44588</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>44593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>44593</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>44594</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>44599</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>44606</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>44606</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>44607</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>44607</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>44607</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>44609</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44609</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44609</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44609</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44613</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>44613</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>44621</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44621</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44624</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44626</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44636</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44636</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44638</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44638</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>44638</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>44638</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44638</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>44641</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>44642</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>44648</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>44649</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>44655</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>44655</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>44655</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>44656</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44656</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44656</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>44657</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44657</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44658</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44658</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>44663</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44663</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>44663</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>44663</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>44663</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>44670</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>44670</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>44672</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>44672</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44674</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>44677</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>44678</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>44678</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44679</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44679</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44685</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44686</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44686</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44692</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44697</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44698</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>44699</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>44705</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>44713</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44715</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44720</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>44724</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44725</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44726</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44733</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44740</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44741</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44749</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44760</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44762</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44763</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44768</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44771</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44771</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44772</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44775</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44776</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44776</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44776</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44781</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44790</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44796</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44800</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44805</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44809</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44809</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44809</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44810</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44810</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44812</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44817</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44823</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44824</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44830</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44831</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44831</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44837</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44837</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44838</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44838</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32531,7 +32531,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>44839</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44841</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44845</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44846</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44847</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44852</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44854</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44858</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44858</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44859</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44861</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44861</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44868</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44869</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44873</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44879</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44880</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44880</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>44881</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>44881</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44881</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>44881</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44882</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>44882</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44882</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>44882</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>44882</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44882</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44883</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44887</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44887</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>44887</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>44888</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>44893</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44893</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44893</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>44894</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>44894</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44895</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44895</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>44896</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>44896</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>44908</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>44908</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>44909</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>44911</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>44914</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>44916</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>44916</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>44917</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44929</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44931</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44944</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44945</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>44945</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44945</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44947</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44947</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44951</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>44951</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>44959</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>44959</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>44959</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>44959</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44959</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>44961</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>44964</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44965</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44966</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44967</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44967</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>44970</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>44971</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44971</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44971</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>44971</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>44971</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>44977</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>44978</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>44992</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>44994</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>44999</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45002</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45002</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45002</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45006</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45006</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45006</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45007</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45008</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45008</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45009</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45015</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45021</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45022</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45022</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45033</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45033</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45035</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>45038</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>45038</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>45038</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>45038</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>45040</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45041</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45042</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45043</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45043</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45043</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45043</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45048</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>45053</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45059</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45062</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>45068</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>45068</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45069</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45069</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45070</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45070</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45070</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45070</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45070</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45070</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45071</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45071</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45071</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45072</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45075</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45078</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45079</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45084</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45084</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45084</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45084</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45084</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>45084</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>45085</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45085</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45087</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45087</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>45087</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45087</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45089</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45091</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45092</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45092</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45093</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45093</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45097</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>45099</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45104</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45104</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45104</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45112</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45114</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45120</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45124</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45132</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45132</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45133</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45134</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45134</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45134</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45134</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45134</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45134</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45134</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45134</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45139</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45140</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45140</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45140</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45140</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45140</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45140</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45141</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45147</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45147</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>45152</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45153</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45153</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45154</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45154</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45155</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45157</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45157</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45157</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45158</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45159</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45159</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45160</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45160</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45161</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45161</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45161</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45161</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45162</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45162</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>45162</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45162</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45162</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45788,7 +45788,7 @@
         <v>45162</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>45162</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>45162</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45162</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45162</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>45162</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45162</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46187,7 +46187,7 @@
         <v>45162</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>45163</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45163</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45163</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>45163</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45163</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45163</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>45163</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45166</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46700,7 +46700,7 @@
         <v>45166</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>45166</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45166</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45166</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45166</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45166</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45167</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45167</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45167</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45167</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45168</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45168</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45168</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>45169</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>45170</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45173</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45173</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45173</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45173</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>45173</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45174</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47897,7 +47897,7 @@
         <v>45176</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47954,7 +47954,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48068,7 +48068,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>45176</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45180</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>45182</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45187</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45189</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45189</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45190</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45190</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>45190</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49151,7 +49151,7 @@
         <v>45191</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49208,7 +49208,7 @@
         <v>45194</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45194</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45194</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45194</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45199</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45199</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45203</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49897,7 +49897,7 @@
         <v>45209</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45211</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>45211</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>45212</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50125,7 +50125,7 @@
         <v>45215</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45217</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50296,7 +50296,7 @@
         <v>45217</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>45217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50638,7 +50638,7 @@
         <v>45222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>45223</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50866,7 +50866,7 @@
         <v>45224</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>45224</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>45224</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45224</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>45225</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45225</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45225</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51265,7 +51265,7 @@
         <v>45225</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45225</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>45225</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45225</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51493,7 +51493,7 @@
         <v>45225</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45225</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45226</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45227</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>45227</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51778,7 +51778,7 @@
         <v>45227</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45227</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>45227</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51949,7 +51949,7 @@
         <v>45227</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52006,7 +52006,7 @@
         <v>45230</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>45230</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52120,7 +52120,7 @@
         <v>45231</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52182,7 +52182,7 @@
         <v>45231</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45231</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>45231</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45231</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45233</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52472,7 +52472,7 @@
         <v>45233</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52529,7 +52529,7 @@
         <v>45233</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         <v>45233</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>45233</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45233</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45233</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>45233</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>45233</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45236</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
         <v>45236</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>45236</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>45236</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53156,7 +53156,7 @@
         <v>45236</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>45236</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53270,7 +53270,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53327,7 +53327,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53384,7 +53384,7 @@
         <v>45236</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53441,7 +53441,7 @@
         <v>45236</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53498,7 +53498,7 @@
         <v>45237</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>45237</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45237</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53669,7 +53669,7 @@
         <v>45237</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>45237</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53776,14 +53776,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 55765-2023</t>
+          <t>A 55763-2023</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53833,14 +53833,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 55763-2023</t>
+          <t>A 55765-2023</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53897,7 +53897,7 @@
         <v>45242</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>45242</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>45243</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54061,14 +54061,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 56775-2023</t>
+          <t>A 56717-2023</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -54118,14 +54118,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 56780-2023</t>
+          <t>A 56772-2023</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54138,7 +54138,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -54175,14 +54175,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 56784-2023</t>
+          <t>A 56776-2023</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54195,7 +54195,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -54232,14 +54232,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 56796-2023</t>
+          <t>A 56793-2023</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54289,14 +54289,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 56804-2023</t>
+          <t>A 56775-2023</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54346,14 +54346,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 56717-2023</t>
+          <t>A 56780-2023</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54403,14 +54403,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 56772-2023</t>
+          <t>A 56784-2023</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54460,14 +54460,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 56776-2023</t>
+          <t>A 56796-2023</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54517,14 +54517,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 56793-2023</t>
+          <t>A 56804-2023</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54581,7 +54581,7 @@
         <v>45244</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54695,7 +54695,7 @@
         <v>45244</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>45244</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>45244</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45244</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45244</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45244</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55030,14 +55030,14 @@
     <row r="941" ht="15" customHeight="1">
       <c r="A941" t="inlineStr">
         <is>
-          <t>A 57170-2023</t>
+          <t>A 57173-2023</t>
         </is>
       </c>
       <c r="B941" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="H941" t="n">
         <v>0</v>
@@ -55087,14 +55087,14 @@
     <row r="942" ht="15" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>A 57173-2023</t>
+          <t>A 57170-2023</t>
         </is>
       </c>
       <c r="B942" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -55144,14 +55144,14 @@
     <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
-          <t>A 57196-2023</t>
+          <t>A 57204-2023</t>
         </is>
       </c>
       <c r="B943" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -55201,14 +55201,14 @@
     <row r="944" ht="15" customHeight="1">
       <c r="A944" t="inlineStr">
         <is>
-          <t>A 57215-2023</t>
+          <t>A 57196-2023</t>
         </is>
       </c>
       <c r="B944" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -55258,14 +55258,14 @@
     <row r="945" ht="15" customHeight="1">
       <c r="A945" t="inlineStr">
         <is>
-          <t>A 57204-2023</t>
+          <t>A 57215-2023</t>
         </is>
       </c>
       <c r="B945" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         </is>
       </c>
       <c r="G945" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -55315,14 +55315,14 @@
     <row r="946" ht="15" customHeight="1">
       <c r="A946" t="inlineStr">
         <is>
-          <t>A 57562-2023</t>
+          <t>A 58406-2023</t>
         </is>
       </c>
       <c r="B946" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         </is>
       </c>
       <c r="G946" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -55372,14 +55372,14 @@
     <row r="947" ht="15" customHeight="1">
       <c r="A947" t="inlineStr">
         <is>
-          <t>A 57571-2023</t>
+          <t>A 57562-2023</t>
         </is>
       </c>
       <c r="B947" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         </is>
       </c>
       <c r="G947" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -55429,14 +55429,14 @@
     <row r="948" ht="15" customHeight="1">
       <c r="A948" t="inlineStr">
         <is>
-          <t>A 58406-2023</t>
+          <t>A 57571-2023</t>
         </is>
       </c>
       <c r="B948" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -55486,14 +55486,14 @@
     <row r="949" ht="15" customHeight="1">
       <c r="A949" t="inlineStr">
         <is>
-          <t>A 57854-2023</t>
+          <t>A 57917-2023</t>
         </is>
       </c>
       <c r="B949" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -55543,14 +55543,14 @@
     <row r="950" ht="15" customHeight="1">
       <c r="A950" t="inlineStr">
         <is>
-          <t>A 57916-2023</t>
+          <t>A 57854-2023</t>
         </is>
       </c>
       <c r="B950" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         </is>
       </c>
       <c r="G950" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="H950" t="n">
         <v>0</v>
@@ -55600,14 +55600,14 @@
     <row r="951" ht="15" customHeight="1">
       <c r="A951" t="inlineStr">
         <is>
-          <t>A 57917-2023</t>
+          <t>A 57916-2023</t>
         </is>
       </c>
       <c r="B951" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         </is>
       </c>
       <c r="G951" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -55657,14 +55657,14 @@
     <row r="952" ht="15" customHeight="1">
       <c r="A952" t="inlineStr">
         <is>
-          <t>A 58283-2023</t>
+          <t>A 58204-2023</t>
         </is>
       </c>
       <c r="B952" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55677,7 +55677,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -55714,14 +55714,14 @@
     <row r="953" ht="15" customHeight="1">
       <c r="A953" t="inlineStr">
         <is>
-          <t>A 58401-2023</t>
+          <t>A 58283-2023</t>
         </is>
       </c>
       <c r="B953" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         </is>
       </c>
       <c r="G953" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -55771,14 +55771,14 @@
     <row r="954" ht="15" customHeight="1">
       <c r="A954" t="inlineStr">
         <is>
-          <t>A 58426-2023</t>
+          <t>A 58401-2023</t>
         </is>
       </c>
       <c r="B954" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         </is>
       </c>
       <c r="G954" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="H954" t="n">
         <v>0</v>
@@ -55828,14 +55828,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 58403-2023</t>
+          <t>A 58426-2023</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -55885,14 +55885,14 @@
     <row r="956" ht="15" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>A 58204-2023</t>
+          <t>A 58403-2023</t>
         </is>
       </c>
       <c r="B956" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -55949,7 +55949,7 @@
         <v>45252</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56006,7 +56006,7 @@
         <v>45252</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>45252</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56170,14 +56170,14 @@
     <row r="961" ht="15" customHeight="1">
       <c r="A961" t="inlineStr">
         <is>
-          <t>A 59802-2023</t>
+          <t>A 59991-2023</t>
         </is>
       </c>
       <c r="B961" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         </is>
       </c>
       <c r="G961" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H961" t="n">
         <v>0</v>
@@ -56227,14 +56227,14 @@
     <row r="962" ht="15" customHeight="1">
       <c r="A962" t="inlineStr">
         <is>
-          <t>A 59991-2023</t>
+          <t>A 59990-2023</t>
         </is>
       </c>
       <c r="B962" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         </is>
       </c>
       <c r="G962" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -56284,14 +56284,14 @@
     <row r="963" ht="15" customHeight="1">
       <c r="A963" t="inlineStr">
         <is>
-          <t>A 59990-2023</t>
+          <t>A 59802-2023</t>
         </is>
       </c>
       <c r="B963" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         </is>
       </c>
       <c r="G963" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H963" t="n">
         <v>0</v>
@@ -56348,7 +56348,7 @@
         <v>45258</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56398,14 +56398,14 @@
     <row r="965" ht="15" customHeight="1">
       <c r="A965" t="inlineStr">
         <is>
-          <t>A 60277-2023</t>
+          <t>A 60084-2023</t>
         </is>
       </c>
       <c r="B965" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56418,7 +56418,7 @@
         </is>
       </c>
       <c r="G965" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -56455,14 +56455,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 60291-2023</t>
+          <t>A 60290-2023</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -56512,14 +56512,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 60084-2023</t>
+          <t>A 60274-2023</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56569,14 +56569,14 @@
     <row r="968" ht="15" customHeight="1">
       <c r="A968" t="inlineStr">
         <is>
-          <t>A 60274-2023</t>
+          <t>A 60293-2023</t>
         </is>
       </c>
       <c r="B968" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         </is>
       </c>
       <c r="G968" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -56626,14 +56626,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 60293-2023</t>
+          <t>A 60277-2023</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -56683,14 +56683,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 60290-2023</t>
+          <t>A 60291-2023</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56747,7 +56747,7 @@
         <v>45259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45259</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45261</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45261</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>45261</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57032,7 +57032,7 @@
         <v>45265</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45265</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57139,14 +57139,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 61647-2023</t>
+          <t>A 61510-2023</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57159,7 +57159,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -57196,14 +57196,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 61510-2023</t>
+          <t>A 61647-2023</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57216,7 +57216,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -57260,7 +57260,7 @@
         <v>45266</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45266</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -564,7 +564,7 @@
         <v>45147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>43802</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>44520</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44585</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>43433</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>43860</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>43860</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44120</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>44449</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44455</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44512</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44690</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44872</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>44879</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45140</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45264</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>43334</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>43334</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>43339</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>43339</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>43348</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>43349</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>43349</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>43353</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>43356</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>43358</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>43360</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>43362</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>43363</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>43377</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>43388</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>43390</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43393</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>43393</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>43395</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>43398</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>43412</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>43418</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>43420</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43425</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>43433</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>43433</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>43433</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>43434</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>43436</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>43442</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>43451</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>43454</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>43462</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>43464</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>43464</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>43464</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>43473</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>43474</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>43475</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>43475</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>43479</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>43479</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>43480</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>43482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>43482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>43485</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>43486</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>43489</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>43494</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>43501</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>43504</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>43507</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>43507</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>43507</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>43510</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>43524</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>43530</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>43532</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>43538</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>43546</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>43556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>43556</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>43578</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>43578</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>43592</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>43594</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>43601</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>43601</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>43602</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>43605</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>43606</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>43608</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>43626</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>43653</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>43662</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>43664</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>43670</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43676</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>43684</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43689</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>43689</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>43690</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>43692</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43700</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43700</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43704</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43705</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43705</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>43705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43705</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>43708</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>43710</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>43726</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43727</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43731</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43731</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43731</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43731</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43739</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43739</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43741</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43745</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43748</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43761</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43765</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43770</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43774</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43774</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43784</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43784</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43786</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43787</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43789</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43795</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43795</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43796</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43796</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43798</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43800</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43829</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43842</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43845</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43846</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43854</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43860</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>43860</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43860</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43861</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43861</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>43865</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43865</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43867</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>43868</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>43868</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43868</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43872</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43878</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43879</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43881</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43882</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43886</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43892</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43893</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43893</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43894</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43899</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43899</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43899</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43901</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43901</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43901</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43902</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43903</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43916</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43920</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43923</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43927</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43929</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43966</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43974</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43974</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43979</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43980</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43986</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43992</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>44004</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44004</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>44010</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44040</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44042</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44046</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>44048</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44048</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44054</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44054</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44055</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44060</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44060</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44062</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44068</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44075</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44082</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44084</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44089</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44090</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44105</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44110</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44116</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44120</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>44125</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44130</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44137</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44138</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44147</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44154</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44160</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44161</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44161</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44161</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44161</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44161</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44164</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44165</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44173</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44175</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44179</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44180</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44181</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44182</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44195</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44195</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44195</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44201</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44201</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44204</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44206</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44206</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44215</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44218</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44218</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44220</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44221</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44229</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44236</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44237</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44238</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44245</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44257</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44257</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44265</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44267</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44267</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44267</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>44270</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>44273</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44280</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44294</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44295</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44299</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44299</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44299</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44299</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44306</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44306</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44306</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44309</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44312</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44312</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>44313</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>44313</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44313</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44314</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44319</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44319</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44320</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44325</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>44333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>44333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>44333</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>44334</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44336</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44349</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44351</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>44354</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44354</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>44368</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>44368</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>44371</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44391</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44391</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44393</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44393</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44403</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44404</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>44412</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>44417</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>44418</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>44419</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44421</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>44439</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>44441</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>44442</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>44442</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44443</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44447</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>44447</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44448</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44448</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44453</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44460</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44462</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>44464</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44469</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44470</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>44474</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44474</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44474</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44474</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>44477</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>44477</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44477</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44480</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>44488</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44488</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44488</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44488</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>44488</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>44488</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>44488</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44490</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44491</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>44497</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44497</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>44497</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>44497</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44501</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>44501</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>44503</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>44506</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44509</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44512</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44512</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44512</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44512</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>44512</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44512</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>44512</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44512</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>44514</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>44515</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44515</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44517</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>44518</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>44520</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>44524</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>44524</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>44530</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>44531</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>44532</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44533</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44533</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44533</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44543</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>44543</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44552</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44553</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44558</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>44565</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>44565</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44566</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44567</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>44567</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>44578</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44579</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44587</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44588</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>44593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>44593</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>44594</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>44599</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>44606</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>44606</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>44607</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>44607</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>44607</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>44609</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44609</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44609</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44609</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44613</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>44613</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>44621</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44621</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44624</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44626</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44636</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44636</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44638</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44638</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>44638</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>44638</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44638</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>44641</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>44642</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>44648</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>44649</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>44655</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>44655</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>44655</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>44656</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44656</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44656</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>44657</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44657</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44658</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44658</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>44663</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44663</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>44663</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>44663</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>44663</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>44670</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>44670</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>44672</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>44672</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44674</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>44677</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>44678</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>44678</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44679</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44679</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44685</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44686</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44686</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44692</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44697</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44698</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>44699</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>44705</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>44713</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44715</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44720</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>44724</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44725</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44726</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44733</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44740</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44741</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44749</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44760</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44762</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44763</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44768</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44771</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44771</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44772</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44775</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44776</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44776</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44776</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44781</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44790</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44796</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44800</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44805</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44809</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44809</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44809</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44810</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44810</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44812</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44817</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44823</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44824</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44830</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44831</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44831</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44837</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44837</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44838</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44838</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32531,7 +32531,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>44839</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44841</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44845</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44846</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44847</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44852</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44854</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44858</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44858</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44859</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44861</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44861</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44868</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44869</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44873</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44879</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44880</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44880</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>44881</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>44881</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44881</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>44881</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44882</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>44882</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44882</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>44882</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>44882</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44882</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44883</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44887</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44887</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>44887</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>44888</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>44893</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44893</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44893</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>44894</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>44894</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44895</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44895</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>44896</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>44896</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>44908</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>44908</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>44909</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>44911</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>44914</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>44916</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>44916</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>44917</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44929</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44931</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44944</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44945</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>44945</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44945</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44947</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44947</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44951</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>44951</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>44959</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>44959</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>44959</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>44959</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44959</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>44961</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>44964</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44965</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44966</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44967</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44967</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>44970</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>44971</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44971</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44971</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>44971</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>44971</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>44977</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>44978</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>44992</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>44994</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>44999</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45002</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45002</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45002</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45006</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45006</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45006</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45007</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45008</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45008</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45009</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45015</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45021</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45022</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45022</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45033</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45033</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45035</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>45038</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>45038</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>45038</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>45038</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>45040</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45041</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45042</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45043</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45043</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45043</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45043</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45048</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>45053</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45059</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45062</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>45068</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>45068</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45069</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45069</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45070</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45070</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45070</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45070</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45070</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45070</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45071</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45071</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45071</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45071</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45072</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45075</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45075</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45075</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45078</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45079</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45084</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45084</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45084</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45084</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45084</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>45084</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>45085</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45085</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45086</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45086</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45086</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45086</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45086</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45087</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45087</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>45087</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45087</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45089</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45089</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45089</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45090</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45091</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45092</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45092</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45093</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>45093</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>45093</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45093</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45093</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45096</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45096</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45097</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45098</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>45099</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45104</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45104</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45104</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45112</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45114</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45120</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45124</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45132</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45132</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45133</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45134</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45134</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45134</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45134</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45134</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45134</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45134</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45134</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45139</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45140</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45140</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45140</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45140</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45140</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45140</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45141</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45147</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45147</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>45152</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45153</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45153</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45154</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45154</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45155</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45157</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45157</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45157</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45158</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45159</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45159</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45160</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45160</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45161</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45161</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45161</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45161</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45162</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45162</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>45162</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45162</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45162</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45788,7 +45788,7 @@
         <v>45162</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>45162</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>45162</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45162</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45162</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>45162</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45162</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46187,7 +46187,7 @@
         <v>45162</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>45163</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45163</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45163</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>45163</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45163</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45163</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>45163</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45166</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46700,7 +46700,7 @@
         <v>45166</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>45166</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45166</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45166</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45166</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45166</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45167</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45167</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45167</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45167</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45168</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>45168</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45168</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>45169</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>45170</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45173</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45173</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45173</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45173</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>45173</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45174</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47897,7 +47897,7 @@
         <v>45176</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47954,7 +47954,7 @@
         <v>45176</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>45176</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48068,7 +48068,7 @@
         <v>45176</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>45176</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>45176</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45180</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45180</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45181</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45181</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>45181</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45181</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45182</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>45182</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45187</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45187</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45187</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45189</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45189</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45190</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45190</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>45190</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49151,7 +49151,7 @@
         <v>45191</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49208,7 +49208,7 @@
         <v>45194</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45194</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45194</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45194</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45199</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45199</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45199</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45203</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49897,7 +49897,7 @@
         <v>45209</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45211</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>45211</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>45212</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50125,7 +50125,7 @@
         <v>45215</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45217</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50296,7 +50296,7 @@
         <v>45217</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>45217</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50638,7 +50638,7 @@
         <v>45222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>45223</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50866,7 +50866,7 @@
         <v>45224</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>45224</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>45224</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45224</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>45225</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45225</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45225</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51265,7 +51265,7 @@
         <v>45225</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45225</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>45225</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45225</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51493,7 +51493,7 @@
         <v>45225</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45225</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45226</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45227</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>45227</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51778,7 +51778,7 @@
         <v>45227</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45227</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>45227</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51949,7 +51949,7 @@
         <v>45227</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52006,7 +52006,7 @@
         <v>45230</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>45230</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52120,7 +52120,7 @@
         <v>45231</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52182,7 +52182,7 @@
         <v>45231</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45231</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>45231</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45231</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45233</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52472,7 +52472,7 @@
         <v>45233</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52529,7 +52529,7 @@
         <v>45233</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         <v>45233</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>45233</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45233</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45233</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>45233</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>45233</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45236</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
         <v>45236</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>45236</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>45236</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53156,7 +53156,7 @@
         <v>45236</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>45236</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53270,7 +53270,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53327,7 +53327,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53384,7 +53384,7 @@
         <v>45236</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53441,7 +53441,7 @@
         <v>45236</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53498,7 +53498,7 @@
         <v>45237</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>45237</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45237</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53669,7 +53669,7 @@
         <v>45237</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>45237</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53776,14 +53776,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 55763-2023</t>
+          <t>A 55765-2023</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53833,14 +53833,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 55765-2023</t>
+          <t>A 55763-2023</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53897,7 +53897,7 @@
         <v>45242</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>45242</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>45243</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>45244</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45244</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54182,7 +54182,7 @@
         <v>45244</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54232,14 +54232,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 56793-2023</t>
+          <t>A 56779-2023</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -54289,14 +54289,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 56775-2023</t>
+          <t>A 56791-2023</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -54346,14 +54346,14 @@
     <row r="929" ht="15" customHeight="1">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A 56780-2023</t>
+          <t>A 56778-2023</t>
         </is>
       </c>
       <c r="B929" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -54403,14 +54403,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 56784-2023</t>
+          <t>A 56786-2023</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -54460,14 +54460,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 56796-2023</t>
+          <t>A 56794-2023</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -54517,14 +54517,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 56804-2023</t>
+          <t>A 56802-2023</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -54574,14 +54574,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 56779-2023</t>
+          <t>A 56793-2023</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -54631,14 +54631,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 56791-2023</t>
+          <t>A 56795-2023</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -54688,14 +54688,14 @@
     <row r="935" ht="15" customHeight="1">
       <c r="A935" t="inlineStr">
         <is>
-          <t>A 56795-2023</t>
+          <t>A 56799-2023</t>
         </is>
       </c>
       <c r="B935" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="H935" t="n">
         <v>0</v>
@@ -54745,14 +54745,14 @@
     <row r="936" ht="15" customHeight="1">
       <c r="A936" t="inlineStr">
         <is>
-          <t>A 56799-2023</t>
+          <t>A 56775-2023</t>
         </is>
       </c>
       <c r="B936" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H936" t="n">
         <v>0</v>
@@ -54802,14 +54802,14 @@
     <row r="937" ht="15" customHeight="1">
       <c r="A937" t="inlineStr">
         <is>
-          <t>A 56778-2023</t>
+          <t>A 56780-2023</t>
         </is>
       </c>
       <c r="B937" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         </is>
       </c>
       <c r="G937" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="H937" t="n">
         <v>0</v>
@@ -54859,14 +54859,14 @@
     <row r="938" ht="15" customHeight="1">
       <c r="A938" t="inlineStr">
         <is>
-          <t>A 56786-2023</t>
+          <t>A 56784-2023</t>
         </is>
       </c>
       <c r="B938" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         </is>
       </c>
       <c r="G938" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H938" t="n">
         <v>0</v>
@@ -54916,14 +54916,14 @@
     <row r="939" ht="15" customHeight="1">
       <c r="A939" t="inlineStr">
         <is>
-          <t>A 56794-2023</t>
+          <t>A 56796-2023</t>
         </is>
       </c>
       <c r="B939" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -54973,14 +54973,14 @@
     <row r="940" ht="15" customHeight="1">
       <c r="A940" t="inlineStr">
         <is>
-          <t>A 56802-2023</t>
+          <t>A 56804-2023</t>
         </is>
       </c>
       <c r="B940" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -55037,7 +55037,7 @@
         <v>45245</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55087,14 +55087,14 @@
     <row r="942" ht="15" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>A 57170-2023</t>
+          <t>A 57215-2023</t>
         </is>
       </c>
       <c r="B942" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -55144,14 +55144,14 @@
     <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
-          <t>A 57204-2023</t>
+          <t>A 57170-2023</t>
         </is>
       </c>
       <c r="B943" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -55201,14 +55201,14 @@
     <row r="944" ht="15" customHeight="1">
       <c r="A944" t="inlineStr">
         <is>
-          <t>A 57196-2023</t>
+          <t>A 57204-2023</t>
         </is>
       </c>
       <c r="B944" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -55258,14 +55258,14 @@
     <row r="945" ht="15" customHeight="1">
       <c r="A945" t="inlineStr">
         <is>
-          <t>A 57215-2023</t>
+          <t>A 57196-2023</t>
         </is>
       </c>
       <c r="B945" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         </is>
       </c>
       <c r="G945" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -55315,14 +55315,14 @@
     <row r="946" ht="15" customHeight="1">
       <c r="A946" t="inlineStr">
         <is>
-          <t>A 58406-2023</t>
+          <t>A 57562-2023</t>
         </is>
       </c>
       <c r="B946" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         </is>
       </c>
       <c r="G946" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -55372,14 +55372,14 @@
     <row r="947" ht="15" customHeight="1">
       <c r="A947" t="inlineStr">
         <is>
-          <t>A 57562-2023</t>
+          <t>A 57571-2023</t>
         </is>
       </c>
       <c r="B947" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         </is>
       </c>
       <c r="G947" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -55429,14 +55429,14 @@
     <row r="948" ht="15" customHeight="1">
       <c r="A948" t="inlineStr">
         <is>
-          <t>A 57571-2023</t>
+          <t>A 58406-2023</t>
         </is>
       </c>
       <c r="B948" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -55486,14 +55486,14 @@
     <row r="949" ht="15" customHeight="1">
       <c r="A949" t="inlineStr">
         <is>
-          <t>A 57917-2023</t>
+          <t>A 57854-2023</t>
         </is>
       </c>
       <c r="B949" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -55543,14 +55543,14 @@
     <row r="950" ht="15" customHeight="1">
       <c r="A950" t="inlineStr">
         <is>
-          <t>A 57854-2023</t>
+          <t>A 57916-2023</t>
         </is>
       </c>
       <c r="B950" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         </is>
       </c>
       <c r="G950" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="H950" t="n">
         <v>0</v>
@@ -55600,14 +55600,14 @@
     <row r="951" ht="15" customHeight="1">
       <c r="A951" t="inlineStr">
         <is>
-          <t>A 57916-2023</t>
+          <t>A 57917-2023</t>
         </is>
       </c>
       <c r="B951" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         </is>
       </c>
       <c r="G951" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -55657,14 +55657,14 @@
     <row r="952" ht="15" customHeight="1">
       <c r="A952" t="inlineStr">
         <is>
-          <t>A 58204-2023</t>
+          <t>A 58283-2023</t>
         </is>
       </c>
       <c r="B952" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55677,7 +55677,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -55714,14 +55714,14 @@
     <row r="953" ht="15" customHeight="1">
       <c r="A953" t="inlineStr">
         <is>
-          <t>A 58283-2023</t>
+          <t>A 58403-2023</t>
         </is>
       </c>
       <c r="B953" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         </is>
       </c>
       <c r="G953" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -55778,7 +55778,7 @@
         <v>45250</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -55835,7 +55835,7 @@
         <v>45250</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -55885,14 +55885,14 @@
     <row r="956" ht="15" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>A 58403-2023</t>
+          <t>A 58204-2023</t>
         </is>
       </c>
       <c r="B956" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -55942,14 +55942,14 @@
     <row r="957" ht="15" customHeight="1">
       <c r="A957" t="inlineStr">
         <is>
-          <t>A 58917-2023</t>
+          <t>A 59075-2023</t>
         </is>
       </c>
       <c r="B957" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="H957" t="n">
         <v>0</v>
@@ -55999,14 +55999,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 59036-2023</t>
+          <t>A 58917-2023</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56056,14 +56056,14 @@
     <row r="959" ht="15" customHeight="1">
       <c r="A959" t="inlineStr">
         <is>
-          <t>A 59075-2023</t>
+          <t>A 59036-2023</t>
         </is>
       </c>
       <c r="B959" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         </is>
       </c>
       <c r="G959" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="H959" t="n">
         <v>0</v>
@@ -56120,7 +56120,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56170,14 +56170,14 @@
     <row r="961" ht="15" customHeight="1">
       <c r="A961" t="inlineStr">
         <is>
-          <t>A 59991-2023</t>
+          <t>A 59802-2023</t>
         </is>
       </c>
       <c r="B961" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         </is>
       </c>
       <c r="G961" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="H961" t="n">
         <v>0</v>
@@ -56227,14 +56227,14 @@
     <row r="962" ht="15" customHeight="1">
       <c r="A962" t="inlineStr">
         <is>
-          <t>A 59990-2023</t>
+          <t>A 59991-2023</t>
         </is>
       </c>
       <c r="B962" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         </is>
       </c>
       <c r="G962" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -56284,14 +56284,14 @@
     <row r="963" ht="15" customHeight="1">
       <c r="A963" t="inlineStr">
         <is>
-          <t>A 59802-2023</t>
+          <t>A 59990-2023</t>
         </is>
       </c>
       <c r="B963" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         </is>
       </c>
       <c r="G963" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H963" t="n">
         <v>0</v>
@@ -56348,7 +56348,7 @@
         <v>45258</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45258</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45258</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56512,14 +56512,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 60274-2023</t>
+          <t>A 60293-2023</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56569,14 +56569,14 @@
     <row r="968" ht="15" customHeight="1">
       <c r="A968" t="inlineStr">
         <is>
-          <t>A 60293-2023</t>
+          <t>A 60277-2023</t>
         </is>
       </c>
       <c r="B968" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         </is>
       </c>
       <c r="G968" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -56626,14 +56626,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 60277-2023</t>
+          <t>A 60291-2023</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -56683,14 +56683,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 60291-2023</t>
+          <t>A 60274-2023</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56740,14 +56740,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 60340-2023</t>
+          <t>A 60441-2023</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56760,7 +56760,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -56797,14 +56797,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 60441-2023</t>
+          <t>A 60340-2023</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45259</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -56817,7 +56817,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -56861,7 +56861,7 @@
         <v>45261</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45261</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>45261</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57025,14 +57025,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 61508-2023</t>
+          <t>A 61647-2023</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57045,7 +57045,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -57082,14 +57082,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 61512-2023</t>
+          <t>A 61510-2023</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57102,7 +57102,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -57139,14 +57139,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 61510-2023</t>
+          <t>A 61508-2023</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57159,7 +57159,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -57196,14 +57196,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 61647-2023</t>
+          <t>A 61512-2023</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45266</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45266</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -564,7 +564,7 @@
         <v>45147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>43802</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>44520</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>44585</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>43433</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>43438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>43860</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>43860</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44120</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>44449</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44455</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44512</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44690</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44872</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>44879</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45140</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45264</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>43334</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>43334</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>43339</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>43339</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>43346</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>43348</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>43349</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>43349</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>43353</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>43356</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>43358</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>43360</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>43362</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>43363</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>43377</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>43388</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>43390</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43393</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>43393</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>43395</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>43398</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>43412</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>43418</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>43420</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43425</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>43433</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>43433</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>43433</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>43434</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>43436</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>43442</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>43451</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>43454</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>43462</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>43464</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>43464</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>43464</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>43473</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>43474</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>43475</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>43475</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>43479</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>43479</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>43480</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>43482</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>43482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>43485</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>43486</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>43489</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>43494</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>43501</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>43504</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>43507</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>43507</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>43507</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>43510</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>43524</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>43530</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>43532</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>43538</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>43546</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>43556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>43556</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>43578</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>43578</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>43592</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>43594</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>43601</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>43601</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>43602</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>43605</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>43606</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>43608</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>43626</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>43653</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>43662</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>43664</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>43670</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43676</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>43684</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43689</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>43689</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>43690</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>43692</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43700</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43700</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43704</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43705</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43705</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>43705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43705</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>43708</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>43710</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>43726</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43727</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43731</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43731</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43731</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43731</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43739</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43739</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43741</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43745</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43748</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43761</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43765</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43770</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43774</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43774</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43784</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43784</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43786</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43787</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43789</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43795</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43795</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43796</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43796</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43798</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43800</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43829</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43842</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43845</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43846</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43854</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43860</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>43860</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>43860</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43861</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43861</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>43865</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43865</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43867</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>43868</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>43868</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43868</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43872</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43878</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43879</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43881</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43882</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43886</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43886</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43892</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43893</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43893</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43894</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43899</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43899</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43899</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43901</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43901</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43901</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43902</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43903</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>43916</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>43920</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43923</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>43927</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>43929</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>43963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>43966</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43974</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43974</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43979</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43980</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43986</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43992</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>44004</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44004</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>44010</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44040</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44042</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44046</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>44048</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44048</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44054</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44054</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44055</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44060</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44060</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44062</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44068</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44075</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44082</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44084</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44089</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44090</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44105</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44110</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>44110</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44110</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44116</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44120</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>44125</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44130</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44137</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44138</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44147</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44154</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>44160</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44160</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44161</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44161</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44161</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44161</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44161</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44164</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44165</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44173</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44175</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44179</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44180</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44181</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44182</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44195</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44195</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44195</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44201</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44201</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44204</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44206</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44206</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44215</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44218</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44218</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44220</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44221</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44221</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44229</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44236</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44237</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44238</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44245</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44257</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44257</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44265</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44267</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44267</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44267</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>44270</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>44273</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44280</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44294</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44295</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44299</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>44299</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44299</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44299</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44306</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44306</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44306</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44309</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44312</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44312</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>44313</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>44313</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44313</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44314</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44319</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44319</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44320</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44325</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>44333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>44333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>44333</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>44334</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44336</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44349</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44351</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>44354</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44354</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>44368</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>44368</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>44371</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44391</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44391</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44393</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44393</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44393</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44403</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44404</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>44412</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>44417</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>44418</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>44419</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44421</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>44439</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>44441</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>44442</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>44442</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44443</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44447</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>44447</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44448</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44448</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44453</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44460</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44462</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>44464</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44469</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44470</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>44474</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44474</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44474</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44474</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>44477</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>44477</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44477</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44480</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>44488</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44488</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44488</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44488</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>44488</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>44488</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>44488</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44490</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44491</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>44497</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44497</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>44497</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>44497</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44501</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>44501</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>44503</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>44506</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44509</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44512</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44512</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44512</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44512</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>44512</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44512</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>44512</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44512</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>44514</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>44515</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44515</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44517</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>44518</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>44520</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>44524</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>44524</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>44530</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>44531</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>44532</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44533</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44533</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44533</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44543</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>44543</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44552</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44553</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44558</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>44565</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44565</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>44565</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44566</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44567</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>44567</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>44578</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44579</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44587</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44588</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>44593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>44593</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>44594</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>44599</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44606</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>44606</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>44606</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>44607</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>44607</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>44607</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>44609</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44609</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44609</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44609</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44613</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>44613</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>44621</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44621</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44624</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44626</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44636</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44636</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44636</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44638</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44638</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44638</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>44638</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>44638</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44638</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>44641</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>44642</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>44648</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>44649</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>44655</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>44655</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>44655</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>44656</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44656</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44656</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>44657</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44657</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44658</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44658</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>44663</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44663</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>44663</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>44663</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>44663</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>44670</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>44670</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>44672</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>44672</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44674</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>44677</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>44678</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>44678</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44679</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44679</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44685</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44686</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44686</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44692</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44697</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44698</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>44699</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>44705</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>44713</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44715</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44719</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44720</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>44724</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44725</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44726</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44733</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44735</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44740</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44741</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44749</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44750</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44760</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44762</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44763</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44768</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44771</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44771</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44772</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44775</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44776</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44776</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44776</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44781</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44790</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44796</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44800</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44805</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44809</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44809</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44809</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44810</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44810</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44810</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44812</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44817</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44817</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44823</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44824</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44830</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44831</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44831</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44837</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44837</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44838</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44838</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32531,7 +32531,7 @@
         <v>44839</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>44839</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44841</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44845</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44846</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44847</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44852</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44854</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44855</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44858</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44858</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44859</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44861</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44861</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44868</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44868</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44869</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44873</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44879</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44880</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>44880</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>44881</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>44881</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44881</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>44881</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44882</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>44882</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44882</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>44882</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>44882</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44882</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44883</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44887</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44887</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>44887</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>44888</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>44893</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44893</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44893</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>44894</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>44894</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44895</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44895</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>44896</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>44896</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>44908</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>44908</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>44909</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>44911</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>44914</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>44916</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>44916</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>44917</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44929</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44931</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44944</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44945</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>44945</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44945</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44947</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44947</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44951</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44951</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>44951</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>44959</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>44959</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>44959</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>44959</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44959</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>44961</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>44964</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44965</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44966</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44967</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44967</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>44970</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>44971</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44971</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44971</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>44971</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>44971</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>44977</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>44978</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>44992</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>44994</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>44999</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45002</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45002</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45002</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45006</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45006</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45006</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45007</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45008</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45008</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D643" t="inlineS